--- a/Data/PGD/PGD_structuration.xlsx
+++ b/Data/PGD/PGD_structuration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\PGD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A152AD9B-B756-44EB-BD1C-A87CAC2978B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BFE2A8-6BA5-4F88-ABC2-5FE7217FFBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{98FDD2D6-D1A3-4DDF-A839-2A0863A95ED3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{98FDD2D6-D1A3-4DDF-A839-2A0863A95ED3}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2778" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="622">
   <si>
     <t>Financeur</t>
   </si>
@@ -6314,20 +6314,48 @@
       <c r="AQ14" s="1"/>
       <c r="AR14" s="1"/>
       <c r="AS14" s="1"/>
-      <c r="AT14" s="1"/>
-      <c r="AU14" s="1"/>
-      <c r="AV14" s="1"/>
-      <c r="AW14" s="1"/>
-      <c r="AX14" s="1"/>
-      <c r="AY14" s="1"/>
-      <c r="AZ14" s="1"/>
-      <c r="BA14" s="1"/>
-      <c r="BB14" s="1"/>
-      <c r="BC14" s="1"/>
-      <c r="BD14" s="1"/>
-      <c r="BE14" s="1"/>
-      <c r="BF14" s="1"/>
-      <c r="BG14" s="1"/>
+      <c r="AT14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AV14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AW14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AX14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AY14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AZ14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BA14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BC14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BD14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BE14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BF14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BG14" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="BH14" s="1"/>
       <c r="BI14" s="1"/>
       <c r="BJ14" s="1"/>
@@ -6501,20 +6529,48 @@
       <c r="AQ15" s="1"/>
       <c r="AR15" s="1"/>
       <c r="AS15" s="1"/>
-      <c r="AT15" s="1"/>
-      <c r="AU15" s="1"/>
-      <c r="AV15" s="1"/>
-      <c r="AW15" s="1"/>
-      <c r="AX15" s="1"/>
-      <c r="AY15" s="1"/>
-      <c r="AZ15" s="1"/>
-      <c r="BA15" s="1"/>
-      <c r="BB15" s="1"/>
-      <c r="BC15" s="1"/>
-      <c r="BD15" s="1"/>
-      <c r="BE15" s="1"/>
-      <c r="BF15" s="1"/>
-      <c r="BG15" s="1"/>
+      <c r="AT15" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU15" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AV15" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AW15" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AX15" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AY15" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AZ15" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BA15" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB15" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BC15" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BD15" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BE15" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BF15" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BG15" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="BH15" s="1"/>
       <c r="BI15" s="1"/>
       <c r="BJ15" s="1"/>
@@ -6875,20 +6931,48 @@
       <c r="AQ17" s="1"/>
       <c r="AR17" s="1"/>
       <c r="AS17" s="1"/>
-      <c r="AT17" s="1"/>
-      <c r="AU17" s="1"/>
-      <c r="AV17" s="1"/>
-      <c r="AW17" s="1"/>
-      <c r="AX17" s="1"/>
-      <c r="AY17" s="1"/>
-      <c r="AZ17" s="1"/>
-      <c r="BA17" s="1"/>
-      <c r="BB17" s="1"/>
-      <c r="BC17" s="1"/>
-      <c r="BD17" s="1"/>
-      <c r="BE17" s="1"/>
-      <c r="BF17" s="1"/>
-      <c r="BG17" s="1"/>
+      <c r="AT17" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU17" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AV17" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AW17" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AX17" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AY17" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AZ17" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BA17" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB17" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BC17" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BD17" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BE17" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BF17" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BG17" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="BH17" s="1"/>
       <c r="BI17" s="1"/>
       <c r="BJ17" s="1"/>
@@ -7062,20 +7146,48 @@
       <c r="AQ18" s="1"/>
       <c r="AR18" s="1"/>
       <c r="AS18" s="1"/>
-      <c r="AT18" s="1"/>
-      <c r="AU18" s="1"/>
-      <c r="AV18" s="1"/>
-      <c r="AW18" s="1"/>
-      <c r="AX18" s="1"/>
-      <c r="AY18" s="1"/>
-      <c r="AZ18" s="1"/>
-      <c r="BA18" s="1"/>
-      <c r="BB18" s="1"/>
-      <c r="BC18" s="1"/>
-      <c r="BD18" s="1"/>
-      <c r="BE18" s="1"/>
-      <c r="BF18" s="1"/>
-      <c r="BG18" s="1"/>
+      <c r="AT18" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU18" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AV18" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AW18" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AX18" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AY18" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AZ18" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BA18" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB18" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BC18" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BD18" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BE18" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BF18" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BG18" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="BH18" s="1"/>
       <c r="BI18" s="1"/>
       <c r="BJ18" s="1"/>
@@ -7249,20 +7361,48 @@
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
       <c r="AS19" s="1"/>
-      <c r="AT19" s="1"/>
-      <c r="AU19" s="1"/>
-      <c r="AV19" s="1"/>
-      <c r="AW19" s="1"/>
-      <c r="AX19" s="1"/>
-      <c r="AY19" s="1"/>
-      <c r="AZ19" s="1"/>
-      <c r="BA19" s="1"/>
-      <c r="BB19" s="1"/>
-      <c r="BC19" s="1"/>
-      <c r="BD19" s="1"/>
-      <c r="BE19" s="1"/>
-      <c r="BF19" s="1"/>
-      <c r="BG19" s="1"/>
+      <c r="AT19" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU19" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AV19" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AW19" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AX19" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AY19" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AZ19" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BA19" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB19" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BC19" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BD19" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BE19" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BF19" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BG19" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="BH19" s="1"/>
       <c r="BI19" s="1"/>
       <c r="BJ19" s="1"/>
@@ -7436,20 +7576,48 @@
       <c r="AQ20" s="1"/>
       <c r="AR20" s="1"/>
       <c r="AS20" s="1"/>
-      <c r="AT20" s="1"/>
-      <c r="AU20" s="1"/>
-      <c r="AV20" s="1"/>
-      <c r="AW20" s="1"/>
-      <c r="AX20" s="1"/>
-      <c r="AY20" s="1"/>
-      <c r="AZ20" s="1"/>
-      <c r="BA20" s="1"/>
-      <c r="BB20" s="1"/>
-      <c r="BC20" s="1"/>
-      <c r="BD20" s="1"/>
-      <c r="BE20" s="1"/>
-      <c r="BF20" s="1"/>
-      <c r="BG20" s="1"/>
+      <c r="AT20" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU20" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AV20" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AW20" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AX20" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AY20" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AZ20" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BA20" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB20" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BC20" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BD20" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BE20" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BF20" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BG20" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="BH20" s="1"/>
       <c r="BI20" s="1"/>
       <c r="BJ20" s="1"/>
@@ -7623,20 +7791,48 @@
       <c r="AQ21" s="1"/>
       <c r="AR21" s="1"/>
       <c r="AS21" s="1"/>
-      <c r="AT21" s="1"/>
-      <c r="AU21" s="1"/>
-      <c r="AV21" s="1"/>
-      <c r="AW21" s="1"/>
-      <c r="AX21" s="1"/>
-      <c r="AY21" s="1"/>
-      <c r="AZ21" s="1"/>
-      <c r="BA21" s="1"/>
-      <c r="BB21" s="1"/>
-      <c r="BC21" s="1"/>
-      <c r="BD21" s="1"/>
-      <c r="BE21" s="1"/>
-      <c r="BF21" s="1"/>
-      <c r="BG21" s="1"/>
+      <c r="AT21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AV21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AW21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AX21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AY21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AZ21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BA21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BC21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BD21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BE21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BF21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BG21" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="BH21" s="1"/>
       <c r="BI21" s="1"/>
       <c r="BJ21" s="1"/>
@@ -7810,20 +8006,48 @@
       <c r="AQ22" s="1"/>
       <c r="AR22" s="1"/>
       <c r="AS22" s="1"/>
-      <c r="AT22" s="1"/>
-      <c r="AU22" s="1"/>
-      <c r="AV22" s="1"/>
-      <c r="AW22" s="1"/>
-      <c r="AX22" s="1"/>
-      <c r="AY22" s="1"/>
-      <c r="AZ22" s="1"/>
-      <c r="BA22" s="1"/>
-      <c r="BB22" s="1"/>
-      <c r="BC22" s="1"/>
-      <c r="BD22" s="1"/>
-      <c r="BE22" s="1"/>
-      <c r="BF22" s="1"/>
-      <c r="BG22" s="1"/>
+      <c r="AT22" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU22" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AV22" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AW22" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AX22" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AY22" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AZ22" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BA22" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB22" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BC22" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BD22" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BE22" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BF22" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BG22" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="BH22" s="1"/>
       <c r="BI22" s="1"/>
       <c r="BJ22" s="1"/>
@@ -7997,20 +8221,48 @@
       <c r="AQ23" s="1"/>
       <c r="AR23" s="1"/>
       <c r="AS23" s="1"/>
-      <c r="AT23" s="1"/>
-      <c r="AU23" s="1"/>
-      <c r="AV23" s="1"/>
-      <c r="AW23" s="1"/>
-      <c r="AX23" s="1"/>
-      <c r="AY23" s="1"/>
-      <c r="AZ23" s="1"/>
-      <c r="BA23" s="1"/>
-      <c r="BB23" s="1"/>
-      <c r="BC23" s="1"/>
-      <c r="BD23" s="1"/>
-      <c r="BE23" s="1"/>
-      <c r="BF23" s="1"/>
-      <c r="BG23" s="1"/>
+      <c r="AT23" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU23" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AV23" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AW23" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AX23" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AY23" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AZ23" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BA23" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB23" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BC23" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BD23" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BE23" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BF23" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BG23" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="BH23" s="1"/>
       <c r="BI23" s="1"/>
       <c r="BJ23" s="1"/>
@@ -8184,20 +8436,48 @@
       <c r="AQ24" s="1"/>
       <c r="AR24" s="1"/>
       <c r="AS24" s="1"/>
-      <c r="AT24" s="1"/>
-      <c r="AU24" s="1"/>
-      <c r="AV24" s="1"/>
-      <c r="AW24" s="1"/>
-      <c r="AX24" s="1"/>
-      <c r="AY24" s="1"/>
-      <c r="AZ24" s="1"/>
-      <c r="BA24" s="1"/>
-      <c r="BB24" s="1"/>
-      <c r="BC24" s="1"/>
-      <c r="BD24" s="1"/>
-      <c r="BE24" s="1"/>
-      <c r="BF24" s="1"/>
-      <c r="BG24" s="1"/>
+      <c r="AT24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AV24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AW24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AX24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AY24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AZ24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BA24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BC24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BD24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BE24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BF24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BG24" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="BH24" s="1"/>
       <c r="BI24" s="1"/>
       <c r="BJ24" s="1"/>
@@ -8371,24 +8651,48 @@
       <c r="AQ25" s="1"/>
       <c r="AR25" s="1"/>
       <c r="AS25" s="1"/>
-      <c r="AT25" s="1"/>
-      <c r="AU25" s="1"/>
-      <c r="AV25" s="1"/>
-      <c r="AW25" s="1"/>
-      <c r="AX25" s="1"/>
-      <c r="AY25" s="1"/>
-      <c r="AZ25" s="1"/>
+      <c r="AT25" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU25" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AV25" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AW25" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AX25" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AY25" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AZ25" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="BA25" s="1" t="s">
         <v>573</v>
       </c>
       <c r="BB25" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="BC25" s="1"/>
-      <c r="BD25" s="1"/>
-      <c r="BE25" s="1"/>
-      <c r="BF25" s="1"/>
-      <c r="BG25" s="1"/>
+      <c r="BC25" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BD25" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BE25" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BF25" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BG25" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="BH25" s="1" t="s">
         <v>578</v>
       </c>
@@ -10719,20 +11023,48 @@
       <c r="AQ37" s="1"/>
       <c r="AR37" s="1"/>
       <c r="AS37" s="1"/>
-      <c r="AT37" s="1"/>
-      <c r="AU37" s="1"/>
-      <c r="AV37" s="1"/>
-      <c r="AW37" s="1"/>
-      <c r="AX37" s="1"/>
-      <c r="AY37" s="1"/>
-      <c r="AZ37" s="1"/>
-      <c r="BA37" s="1"/>
-      <c r="BB37" s="1"/>
-      <c r="BC37" s="1"/>
-      <c r="BD37" s="1"/>
-      <c r="BE37" s="1"/>
-      <c r="BF37" s="1"/>
-      <c r="BG37" s="1"/>
+      <c r="AT37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AV37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AW37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AX37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AY37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AZ37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BA37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BC37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BD37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BE37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BF37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BG37" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="BH37" s="1"/>
       <c r="BI37" s="1"/>
       <c r="BJ37" s="1"/>

--- a/Data/PGD/PGD_structuration.xlsx
+++ b/Data/PGD/PGD_structuration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\PGD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3822AE05-0072-46FC-8ACE-041B673E8B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DCCD13-3A99-4760-AF28-2FFB9F433EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{98FDD2D6-D1A3-4DDF-A839-2A0863A95ED3}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="804">
   <si>
     <t>Financeur</t>
   </si>
@@ -2948,6 +2948,218 @@
   </si>
   <si>
     <t>/Texte/</t>
+  </si>
+  <si>
+    <t>Le  projet  RIFT  état  un  projet  ciblé  sur  le  renforcement  des  infrastructures  en  région  tropicales  et 
+méditerranéennes, l’observation in situ y est à ce titre au cœur de ses préoccupations. De plus, le projet 
+est centré sur un dispositif de mesure, la Tour de flux, dédié à la mesure quantitative des flux gazeux 
+(CO2 et H2O prioritairement) qui s’échangent entre surface et atmosphère. Les capteurs ne permettant 
+d’accéder seulement qu’à des proxys des flux, pour produire des données de qualité et fiables, il est 
+indispensable de : i) passer par une étape de post traitement des données brutes acquises, ii) d’acquérir 
+en parallèle des données complémentaires sur les conditions climatiques et environnementales</t>
+  </si>
+  <si>
+    <t>Toutes ces données acquises font l’objet d’un GT « Technique » du projet (GT1) car elles sont jugées 
+essentielles et indispensables au projet RIFT. C’est pourquoi l’effort est mis prioritairement à ce stade 
+dans  le  PDG  sur  ce  cercle  de  données.  Un  second  cercle  est  proposé  en  vue  d’une  valorisation 
+scientifique du projet par le consortium, incluant données et produits élaborés par les GT « Science » 
+du projet RIFT (GT 2,3 et 4). Un premier inventaire de ces produits, non exhaustif à ce stade, a été 
+effectué lors du KOM de RIFT, mais certains d’entre eux restent conditionnés à l’acquisition de données 
+complémentaires hors périmètre du projet RIFT ainsi qu’à des développements méthodologiques et 
+numériques. Certains aspects restant à ce stade encore exploratoires et hypothétiques, il est difficile 
+d’en envisager une planification et une gestion précise. Nous proposerons donc une actualisation dans 
+les prochaines versions du PGD, a minima à échéance de la réunion d’avancement à mi-parcours du 
+projet RIFT. 
+A l’échelle du projet, il a été aussi décidé qu’un ensemble de bonnes pratiques seraient partagées afin 
+de :  
+•  Homogénéiser dans la mesure du possible, les données collectées, produites et/ou analysées 
+et aussi de simplifier le traitement automatisé sans perdre de vue leur FAIRisation ; 
+•  Mettre  en  place  des  procédures  de  qualité  communes  et/ou  spécifiques  (pour  les  objets 
+physiques, les jeux de données etc.), avec un retour d’expérience auprès des communautés 
+intéressées ;  
+•  Respecter  un  code  de  conduite  et  les  aspects  règlementaires  (autorisations  des 
+expérimentation, RGPD, conventions inter organismes et propriété intellectuelle</t>
+  </si>
+  <si>
+    <t>Le projet comporte 13 sites sous la coordination des PI de sites recensés dans le projet. Chacun de ces 
+sites  inclut  à minima  un  dispositif  de Tour  de flux,  dont  les  relevés  de  tournées,  les  opérations  de 
+maintenance et de jouvence sont organisées par les équipes en charge des sites. Les sites étant pour 
+une très grande majorité localisée dans des pays étrangers, les PI sites se chargent d’établir, si besoin 
+s’en trouve, une convention d’accueil et de collaboration entre leur institut et les partenaires locaux</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> dans le but d’échantillonner de manière intégrée, à haute fréquence et en 
+continu sur des périodes pluriannuelles</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> variables hydro-micro-météorologiques qui 
+expliquent le comportement thermo-hydrique et biogéochimique des couverts végétaux environnants
+ Des instruments permettant de suivre et caractériser les états de l’environnement proche, des 
+points de vue climatique, thermo-hydrique, radiatif, etc., et ce à une fréquence de l’ordre de la 
+minute. Le croisement de ces informations avec les données de flux permet d’étudier comment 
+le métabolisme de l'écosystème à la base des flux répond aux forçages biophysiques tels que 
+la  lumière, la  température,  la  pluie,  l'humidité  du  sol,  le  CO2, la  phénologie  et/ou  les  traits 
+structurels et fonctionnels des plantes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp;une tour de flux intègre plusieurs capteurs et/ou instruments sur une 
+même structure porteuse,  Des instruments capables de sonder simultanément et à haute fréquence (~20Hz) la covariance 
+des  tourbillons  (i.e. Eddy  covariance,  EC)  et les  concentrations  en  dioxyde  de  carbone,  en 
+vapeur  d’eau,  ainsi  que  la  température, Une tour de flux rassemble donc entre 20 et 30 capteurs, dont le design, la structure, le type et le choix 
+des  capteurs  dépendent  d’une  multitude  autres  éléments  (climat  et  milieu  d’étude,  topographie, 
+ressources, expertise et intérêt thématique du groupe de travail, …). &amp;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Un  post-traitement  des  acquisitions  permet  in  fine 
+d’estimer les échanges de chaleur, de vapeur et de CO2 (donc les flux) qui opèrent entre la 
+surface et l’atmosphère environnante.   Des instruments permettant de suivre et caractériser les états de l’environnement proche, des 
+points de vue climatique, thermo-hydrique, radiatif, etc., et ce à une fréquence de l’ordre de la 
+minute. Le croisement de ces informations avec les données de flux permet d’étudier comment 
+le métabolisme de l'écosystème à la base des flux répond aux forçages biophysiques tels que 
+la  lumière, la  température,  la  pluie,  l'humidité  du  sol,  le  CO2, la  phénologie  et/ou  les  traits 
+structurels et fonctionnels des plantes
+Les  données  de  covariance  acquises  à  20Hz  acquises  seront  traitées  dans  le  but  de  générer  les 
+données de flux sur les 13 sites.  Ces post traitements seront menées soit par les équipes sur place si 
+elles le désirent, ou soit via l’appui de l’ingénieur de recherche qui sera recruté dans le cadre du projet 
+en 2024. L’objectif reste d’avoir une méthode commune et standardisé de post traitement, afin d’être en 
+mesure de délivrer à la fois des chroniques des données de flux standardisées sous un même format, 
+et d’avoir des diagnostiques sur la pertinence des données générées. Cette étape sera réalisée une 
+fois par an à l’aide de la suite logicielle EdiPro, qui est libre de droit de la société CAMPBELL, qui 
+fabrique  des  capteurs  de  flux.  Les  retours  d’expérience  des  personnels  impliqués  sur  les  aspects 
+métrologiques et instrumentaux, et sur les aspects software et post-traitement de la donnée à l’échelle 
+des sites ateliers, seront partagées lors d’atelier et de réunions spécifiques organisées et planifiées 
+dans le GT1. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette diffusion avec FLUXNET reste une incitation très forte et absolument pas une obligation. Ceci s’explique par le fait 
+que les conventions établies entre partenaires sur sites, peuvent inclure des conditions particulières ou 
+des restrictions en lien avec la production et la diffusion des données acquises dans des pays étrangers, 
+ce qui rendrait compliqué, voire impossible, l’établissement de règles communes de diffusion sur tous 
+les sites.   </t>
+  </si>
+  <si>
+    <t>Les données acquises et produits élaborés sur les stations de flux seront prioritairement délivrées dans 
+un format simple d’accès à tous, de type :  
+•  TXT ou CSV pour les métadonnées et séries temporelles.  
+•  JPEG ou TIFF pour les illustrations et les cartes 
+•  PDF pour tous les rapports et délivrables produits.</t>
+  </si>
+  <si>
+    <t>qq 100aines de G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils pourront être de ce fait être facilement échangés entre tous les 
+partenaires, notamment du Sud, sous format ZIP ou RAR.  Des formats plus à vocation scientifique 
+(MAT, NETCDF, GEOTIFF) seront exploités lors des échanges inter-équipes et/ou pour la diffusion vers 
+les bases de données.  </t>
+  </si>
+  <si>
+    <t>&amp;Les métadonnées  seront produites de manière similaire à ce qui est fait dans les observatoires qui 
+incluent les sites de mesure&amp;</t>
+  </si>
+  <si>
+    <t>Une fiche explicative, fournissant des explications sur le site, les materiels 
+déployés, les conditions de mesures, etc. seront aussi fournies pour chaque tour de flux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les données de flux post traitées seront collectées dans l’intention d’être diffusables via le portail de 
+données international FLUXNET qui donne un certain niveau de labélisation de la donnée. La diffusion 
+sous  le  portail  FLUXNET  requiert  la  création  d’un  compte  pour  chaque  PI  de  site,  et l’utilisation  de 
+procédures de formatage et de certification de la donnée.
+Les données de flux extraites de la phase de post traitement seront ensuite exploitées pour produire 
+des d’analyses de certification sur chacun des sites, aussi dans l’idée finale d’établir des diagnostics 
+inter-sites. On s’intéressera de manière commune à tous les sites à :  
+•  La partition des flux de carbone nets de l’écosystème mesurés par les tours, entre flux de nuit 
+et jour pour estimer les composantes GPP et Respiration. Des modèles de respiration seront 
+testés  et  mis  en  œuvre  sur  tous  les  sites,  à  l’aide  des  base  de  données  d’humidité  et  de 
+températures du sol acquises par les tours de flux.  
+•  L’empreinte au sol de la mesure de flux à partir des données de vitesse du vent acquise à la 
+station.  
+•  La correction du flux G à la surface, puis l’évaluation de la fermeture du bilan d’énergie à partir 
+des mesures de flux radiatifs, conductifs et turbulents acquises à la station. 
+</t>
+  </si>
+  <si>
+    <t>Toujours dans l’intention d’harmoniser les procédures de diagnostiques sur chacun des 13 sites, l’apport 
+de la suite logicielle TOVI (https://www.licor.com/env/support/Tovi/home.html) sera testée, en parallèle du 
+développement de routines spécifiques de traitements sous Matlab.</t>
+  </si>
+  <si>
+    <t>es serveurs institutionnels des laboratoires, avec des sauvegardes 
+sur disque dur. Les données seront également regroupées annuellement sur l’espace collaboratif du 
+projet à HydroSciences Montpellier, avec encore double système de sauvegarde : i) en local sur disques 
+durs externes, ii) sur les serveurs de l’UMR avec système de sauvegarde automatique</t>
+  </si>
+  <si>
+    <t>Les données ne sont absolument pas de nature sensible et aucune mesure de sécurité n’est à ce jour 
+envisagée. Si tel était le cas, une note de consentement entre les partenaires devra être établi dans les 
+conventions inter partenaires sur site</t>
+  </si>
+  <si>
+    <t>Trois listes mel ont été créés suite au lancement du projet, en regard des instances de gouvernance du 
+projet :  
+•  Comité exécutif, incluant le porteur, les deux co-porteurs RIFT, le manager du programme FC 
+(soit 4 personnes) ;  
+•  Comité de pilotage, incluant le porteur et les deux co-porteurs RIFT, le manager du programme 
+FC, les PI et co-PI des sites de mesures et les responsables de GT (soit 12 personnes) ; 
+•  Ensemble des membres du projet (soit une 40aine de personnes environ).  
+Ces  listes  sont  gérées  directement  par  le  porteur  du  projet  et  utilisable  par  tous  en  vue  d’une 
+communication interne adaptée. 
+Les pourvoyeurs de données restent propriétaires de l’ensemble des données acquises sur leur site, 
+en respect de la convention qu’ils ont établis entre institutions. Ils s’engagent toutefois dans le cadre du 
+projet, à partager sans délai ces données contractuelles à l’ensemble du consortium RIFT, sur la totalité 
+de la durée du projet, afin de ne pas entraver les étapes de post traitement et de certification de la 
+donnée de flux. Tous les membres du consortium s’engagent à ne pas rediffuser les données acquises 
+sur sites et les post traitements spécifiques aux sites à l’extérieur du consortium, tout du moins sans 
+accord préalable des PI sites et post traitements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toutes les observations listées dans le tableau 1, plus les données de flux issus des post traitements 
+et  de  l’étape  de  certification  finale  du  GT1  seront  bien  entendu  conservées.  Ces  produits  étant  la 
+propriété des sites et des équipes de recherche, ils seront, d’une part, conservés par leur soin sur des 
+espaces de stockage locaux. S’ajoute à ce premier mode de stockage, un moissonnage des données 
+de  flux  certifiés  vers  la  base  de  données  internationale  (FLUXNET)  et  de  l’ensemble  de  données 
+acquises vers les BdD des observatoires auxquels certains sites sont accolés (6 sites sur 13).  
+Concernant les indicateurs, cartes, produits et données complémentaires hautement valorisables du 
+point de vue scientifique, tous issus des WP Sciences, ils seront aussi archivés et sauvegardés, soit 
+dans les bases de données des observatoires quand cela est possible, soit localement chez les équipes 
+en charge de leur production, sur des solutions de type « disque dur externe ». Pour les simulations des 
+modèles les plus importantes, une conservation sur une période d’environ 5 ans est envisagée. En 
+revanche, toutes données de suivi de projet et issus du traitement des données n’ont pas vocation a 
+été gardée au-delà du projet.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerome Demarty (IRD, Jerome.demarty@ird.fr) – PI PGD  
+IR support RIFT (IRD) – PI formatage et archivage des données 
+Chloé. Ollivier (IRD, Chloé.Ollivier@ird.fr) - Gestionnaire Sénégal/Niakhar2 
+Ibrahim Maïnassara (IRD, Ibrahim.Mainassara@ird.fr) – Gestionnaire Niger/Wankama 
+Gilles Boulet (IRD, Gilles.Boulet@ird.fr) – Gestionnaire Inde/Mule Hole 
+Olivier Roupsard (CIRAD, Olivier.Roupsard@cirad.fr) – Gestionnaire Sénégal/Niakhar 
+Valerie le Dantec (Univ Toulouse, valerie.le-dantec@univ-tlse3.fr) - Gestionnaire Tunisie/Taous 
+Ivan Cornu – (CIRAD, Ivan.Cornu@cirad.fr) - Gestionnaire Cameroun/Cacao 
+Rim Zitouna-Chebbi (INRGREF Tunis, rimzitouna@live.fr) - Gestionnaire Tunisie/Kamech 
+Lionel Jarlan (IRD, lionel.jarlan@ird.fr) - Gestionnaires des données Maroc/Tenfit 
+J.-M. Cohard (Univ Grenoble, Jean-Martial.Cohard@univ-grenoble-alpes.fr) - Gestionnaire Bénin 
+Laurent Kerkoat (CNRS, laurent.kergoat@get.omp.eu) – Gestionnaires Sénégal/Ragola 
+Nicolas Barbier (IRD, nicolas.barbier@ird.fr) - Gestionnaires Cameroun/Forêt 
+Joanes Guillemot (CIRAD, joannes.guillemot@cirad.fr) – Gestionnaires Brésil/Mataflux 
+Vincent Blanfort (CIRAD, vincent.blanfort@cirad.fr) – Gestionnaires Guyane/CAARPAG </t>
+  </si>
+  <si>
+    <t>Les ressources financières pour la gestion des données n’ont pas été provisionnée en tant que tel dans 
+le projet RIFT. Toutefois, le recrutement d’un IR sur une durée de 3 ans est prévu dans le cadre du 
+projet, notamment pour travailler sur : i) la mise en place de la suite logicielle EDIPRO qui sera déployée 
+de  manière  commune  à  tous  les  sites,  pour  le  post  traitement  des  données,  ii)  la  génération  de 
+diagnostiques et d’indicateurs d’évaluation de la qualité des données, iii) le formatage et de l’archivage 
+final des données et iv) la formation technique des personnels. Un petit budget a ainsi été provisionné 
+dans RIFT pour assurer le fonctionnement de l’IR, ainsi que la tenue d’un atelier de formation interne 
+sur les aspects production de la donnée (cf. annexe financière). A noter aussi que les moyens généraux 
+et l’émulation interne au comité de pilotage du programme FC seront aussi de bons leviers pour avancer 
+sur tous ces aspects. Enfin, une assistance pourra être demandée aux pôles de données de référence et aux 
+gestionnaires des BBD d’intérêt des SNO présents dans RIFT</t>
   </si>
 </sst>
 </file>
@@ -13888,7 +14100,9 @@
       <c r="E53" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="F53" s="22"/>
+      <c r="F53" s="22" t="s">
+        <v>782</v>
+      </c>
       <c r="G53" s="22" t="s">
         <v>264</v>
       </c>
@@ -13922,7 +14136,9 @@
       <c r="U53" s="22">
         <v>1</v>
       </c>
-      <c r="V53" s="22"/>
+      <c r="V53" s="22" t="s">
+        <v>783</v>
+      </c>
       <c r="W53" s="22" t="s">
         <v>255</v>
       </c>
@@ -13945,9 +14161,15 @@
       <c r="AF53" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="AG53" s="22"/>
-      <c r="AH53" s="22"/>
-      <c r="AI53" s="22"/>
+      <c r="AG53" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="AH53" s="22" t="s">
+        <v>784</v>
+      </c>
+      <c r="AI53" s="22" t="s">
+        <v>785</v>
+      </c>
       <c r="AJ53" s="22"/>
       <c r="AK53" s="22"/>
       <c r="AL53" s="22"/>
@@ -13957,56 +14179,96 @@
       <c r="AP53" s="22"/>
       <c r="AQ53" s="22"/>
       <c r="AR53" s="22"/>
-      <c r="AS53" s="22"/>
-      <c r="AT53" s="22"/>
+      <c r="AS53" s="22" t="s">
+        <v>791</v>
+      </c>
+      <c r="AT53" s="22" t="s">
+        <v>792</v>
+      </c>
       <c r="AU53" s="22"/>
       <c r="AV53" s="22"/>
       <c r="AW53" s="22"/>
       <c r="AX53" s="22"/>
-      <c r="AY53" s="22"/>
-      <c r="AZ53" s="22"/>
+      <c r="AY53" s="22" t="s">
+        <v>787</v>
+      </c>
+      <c r="AZ53" s="22" t="s">
+        <v>786</v>
+      </c>
       <c r="BA53" s="22"/>
-      <c r="BB53" s="22"/>
-      <c r="BC53" s="22"/>
-      <c r="BD53" s="22"/>
+      <c r="BB53" s="22" t="s">
+        <v>791</v>
+      </c>
+      <c r="BC53" s="22" t="s">
+        <v>792</v>
+      </c>
+      <c r="BD53" s="22" t="s">
+        <v>788</v>
+      </c>
       <c r="BE53" s="22"/>
-      <c r="BF53" s="22"/>
-      <c r="BG53" s="22"/>
-      <c r="BH53" s="22"/>
+      <c r="BF53" s="22" t="s">
+        <v>802</v>
+      </c>
+      <c r="BG53" s="22" t="s">
+        <v>803</v>
+      </c>
+      <c r="BH53" s="22" t="s">
+        <v>795</v>
+      </c>
       <c r="BI53" s="22"/>
       <c r="BJ53" s="22"/>
-      <c r="BK53" s="22"/>
-      <c r="BL53" s="22"/>
+      <c r="BK53" s="22" t="s">
+        <v>794</v>
+      </c>
+      <c r="BL53" s="22" t="s">
+        <v>797</v>
+      </c>
       <c r="BM53" s="22"/>
       <c r="BN53" s="22"/>
-      <c r="BO53" s="22"/>
+      <c r="BO53" s="22" t="s">
+        <v>796</v>
+      </c>
       <c r="BP53" s="22"/>
       <c r="BQ53" s="22"/>
-      <c r="BR53" s="22"/>
+      <c r="BR53" s="22" t="s">
+        <v>800</v>
+      </c>
       <c r="BS53" s="22"/>
       <c r="BT53" s="22"/>
       <c r="BU53" s="22"/>
-      <c r="BV53" s="22"/>
+      <c r="BV53" s="22" t="s">
+        <v>789</v>
+      </c>
       <c r="BW53" s="22"/>
       <c r="BX53" s="22"/>
       <c r="BY53" s="22"/>
       <c r="BZ53" s="22"/>
       <c r="CA53" s="22"/>
       <c r="CB53" s="22"/>
-      <c r="CC53" s="22"/>
-      <c r="CD53" s="22"/>
+      <c r="CC53" s="22" t="s">
+        <v>798</v>
+      </c>
+      <c r="CD53" s="22" t="s">
+        <v>799</v>
+      </c>
       <c r="CE53" s="22"/>
       <c r="CF53" s="22"/>
       <c r="CG53" s="22"/>
-      <c r="CH53" s="22"/>
+      <c r="CH53" s="22" t="s">
+        <v>790</v>
+      </c>
       <c r="CI53" s="22"/>
       <c r="CJ53" s="22"/>
       <c r="CK53" s="22"/>
-      <c r="CL53" s="22"/>
+      <c r="CL53" s="22" t="s">
+        <v>793</v>
+      </c>
       <c r="CM53" s="22"/>
       <c r="CN53" s="22"/>
       <c r="CO53" s="22"/>
-      <c r="CP53" s="22"/>
+      <c r="CP53" s="22" t="s">
+        <v>801</v>
+      </c>
       <c r="CQ53" s="22"/>
       <c r="CR53" s="22"/>
       <c r="CS53" s="22"/>

--- a/Data/PGD/PGD_structuration.xlsx
+++ b/Data/PGD/PGD_structuration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\PGD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6332B849-BFD6-4142-8F8A-60D568144971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D91F32-CF87-4C37-923C-D19C33E8FDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{98FDD2D6-D1A3-4DDF-A839-2A0863A95ED3}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2770" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2929" uniqueCount="1020">
   <si>
     <t>Financeur</t>
   </si>
@@ -4254,6 +4254,581 @@
   </si>
   <si>
     <t>DMP Opidor</t>
+  </si>
+  <si>
+    <t>Les	forêts	sont	à	la	fois	fortement	affectées	par	les	changements
+climatiques	en	cours	et	au	coeur	de	la	stratégie	d’atténuation	de	ces
+changements.	Une	meilleure	compréhension	des	effets	du	climat	sur	le
+puits	de	carbone	des	forêts	est	donc	un	enjeu	urgent,	tant	pour	les
+scientifiques	que	pour	les	gestionnaires	forestiers.	Dans	le	projet
+Drought-ForC,	nous	avons	identifié	trois	questions	scientifiques
+majeures	qui	limitent	notre	capacité	à	faire	des	projections	du	puits	de
+carbone	des	forêts	soumises	au	climat	futur.	La	première	concerne
+l’allocation	du	carbone	parmi	les	différents	organes	des	arbres	et	le
+lien	entre	assimilation	photosynthétique	et	séquestration	du	carbone
+dans	les	organes	pérennes.	La	seconde	concerne	la	dégradation	de	la
+matière	organique	et	la	séquestration	du	carbone	dans	le	sol	sous	les
+effets	antagonistes	du	réchauffement	et	de	l’assèchement	des	sols.	La
+troisième	concerne	les	effets	du	déficit	hydrique	sur	la	nutrition
+minérale	et	ses	conséquences	pour	la	croissance	et	le	fonctionnement
+des	arbres.	Le	projet	vise	à	étudier	ces	questions	en	réunissant	tous	les
+sites	forestiers	français	des	infrastructures	ICOS	et	AnaEE	qui
+mesurent	les	flux	de	carbone	par	la	technique	des	corrélations
+turbulentes	ou	utilisent	des	expérimentations	de	manipulation	des
+pluies	in	situ,	ainsi	qu’un	large	consortium	de	modélisateurs	utilisant
+des	modèles	basés	sur	les	processus.	Il	utilisera	à	la	fois	des	données
+déjà	acquises	sur	chacun	des	sites	forestiers,	de	nouveaux	dispositifs
+expérimentaux,	et	un	large	éventail	d’approches	de	modélisation	pour
+mieux	comprendre	les	mécanismes	de	réponse	des	forêts	aux
+changements	climatiques,	quantifier	leurs	impacts	sur	le	bilan	de
+carbone	et	améliorer	les	projections	en	climat	futur.	Le	projet	est
+organisé	en	trois	thèmes	de	recherche	centrés	sur	les	questions
+scientifiques	et	destinés	à	améliorer	nos	connaissances	(l’allocation	du
+carbone,	la	dégradation	de	la	matière	organique	au	sol,	les	limitations
+nutritives),	et	deux	axes	de	travail	transversaux	conçus	pour	améliorer
+l’intégration	des	outils	disponibles	pour	étudier	ces	questions	(c’est	à
+dire	les	expérimentations	de	terrain	et	les	modèles	mécanistes).	Le	lot
+1	consistera	à	homogénéiser	les	protocoles	et	jeux	de	données	entre
+les	sites	et	à	mettre	en	place	la	première	expérience	de	réchauffement
+du	sol	en	forêt	en	France.	Le	lot	2	étudiera	l’effet	de	la	sécheresse	sur
+le	lien	entre	assimilation	et	séquestration	du	carbone,	et	sur
+l’allocation	entre	les	différents	organes	des	arbres.	Le	lot	3	étudiera	la
+dégradation	de	la	matière	organique	du	sol	sous	l’effet	de	la
+sécheresse	et	du	réchauffement,	en	intégrant	les	effets	sur	le
+fonctionnement	biologique	du	sol.	Le	lot	4	étudiera	les	limitations
+nutritives,	le	recyclage	des	nutriments	et	leurs	effets	sur	la	croissance.
+Le	lot	5	consistera	à	valider	les	modèles	sur	les	données
+expérimentales,	à	projeter	les	réponses	sous	des	scénarios	de	climat
+futur	et	à	améliorer	la	modélisation	du	cycle	des	nutriments.	Drought-
+ForC	est	un	projet	fédérateur	ambitieux	qui	reposera	sur	8	sites
+forestiers	français	emblématiques	(5	appartenant	à	ICOS	et	4	à
+AnaEE),	12	modèles	basés	sur	les	processus	et	travaillant	à	des
+échelles	de	temps	et	d’espace	différentes,	et	le	travail	de	25
+chercheurs	issus	de	10	laboratoires.	Le	projet	est	conçu	pour
+permettre	un	meilleur	transfert	des	connaissances	expérimentales	vers
+les	modèles	et	favoriser	l’intégration	des	dispositifs	expérimentaux	et
+des	modèles	à	l'échelle	nationale</t>
+  </si>
+  <si>
+    <t>Protocoles	expérimentaux	décrivant:
+Les	expériences	de	manipulation	des	pluies	dans	les	sites	de	Puéchabon,	Font-Blanche,
+O3HP	et	Montiers
+Les	mesures	environnementales	et	écophysiologiques	mesurées	dans	l'ensemble	des	8
+sites	expérimentaux	du	projet
+Les	mesures	à	mettre	en	oeuvre	pour	les	différents	groupes	de	travail	du	projet	Drought
+ForC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Exclusion	de	pluie,	Météorologie,	Protocoles	de	mesure</t>
+  </si>
+  <si>
+    <t>Les	descriptions	des	protocoles	d'exclusion	de	pluie	et	des	données	environnementales	et
+écophysiologiques	produites	sur	chacun	des	sites	expérimentaux	du	projet	seront	basées	sur	les
+données	existantes	de	chacun	de	groupes	de	recherche	qui	maintiennent	ces	dispositifs
+expérimentaux</t>
+  </si>
+  <si>
+    <t>Protocoles	ICOS	:	http://www.icos-etc.eu/icos/documents/instructions
+Protocoles	AnaEE	France</t>
+  </si>
+  <si>
+    <t>&amp;Expertise	des	chercheurs	impliqués, Les	protocoles	expérimentaux	seront	rédigés	par	les	chercheurs	et	ingénieurs	impliqués	dans	le
+projet	selon	leur	expertise	des	dispositifs	expérimentaux	et	des	méthodes	de	mesure&amp;</t>
+  </si>
+  <si>
+    <t>&amp;Les	protocoles	seront	organisés	par	site	expérimental	et/ou	par	méthode	employée.	Ils	seront
+rédigés	en	français	ou	en	anglais&amp;</t>
+  </si>
+  <si>
+    <t>&amp;Relecture	par	les	pairs&amp;</t>
+  </si>
+  <si>
+    <t>Librement	accessible	(Licence	Ouverte	d'Etalab	ou	CC_BY)	et	sans	contrainte	juridique</t>
+  </si>
+  <si>
+    <t>&amp;Stockage	local	des	informations	par	les	groupes	qui	rédigeront	les	documents	+	stockage
+commun	dans	un	espace	de	travail	partagé	(type	cloud)&amp;</t>
+  </si>
+  <si>
+    <t>100 Mo</t>
+  </si>
+  <si>
+    <t>&amp;double sauvegarde&amp;</t>
+  </si>
+  <si>
+    <t>doc ou pdf</t>
+  </si>
+  <si>
+    <t>Données	environnementales	et	écophysiologiques	dont	la	collecte	a	débuté	avant	le	projet
+Drought	ForC,	et	est	réalisée	par	les	chercheurs	et	personnels	techniques	des	8	sites
+expérimentaux	du	projet,	et	permet	de	suivre	sur	le	long-terme	l'impact	des	dispositifs
+expérimentaux	sur	la	sécheresse	et	le	fonctionnement	des	arbres	et	de	l'écosystème	forestier</t>
+  </si>
+  <si>
+    <t>donnée	météorologique	(Thésaurus	INRAE)
+sol	(Thésaurus	INRAE)
+eau	du	sol	(Thésaurus	INRAE)
+carbone	(Thésaurus	INRAE)
+accroissement	de	la	biomasse	(Thésaurus	INRAE)
+écophysiologie	forestière	(Thésaurus	INRAE)
+propriété	physico-chimique	du	sol	(Thésaurus	INRAE)
+analyse	chimique	(Thésaurus	INRAE</t>
+  </si>
+  <si>
+    <t>Thesaurus Inrae</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Météorologie,	Flux	de	carbone,	Flux	d'eau,	Sol,	Croissance,	Traits	végétaux,	Chimie	du	sol,
+Interopérabilité,	Référentiels	sémantiques</t>
+  </si>
+  <si>
+    <t>&amp;Les	données	de	ce	produit	de	recherche	sont	exclusivement	des	données	existantes	et	ré-
+utilisées	dans	la	cadre	du	projet&amp;</t>
+  </si>
+  <si>
+    <t>observation</t>
+  </si>
+  <si>
+    <t>Interopérabilité	sémantique	:	https://hal.inrae.fr/hal-03579553</t>
+  </si>
+  <si>
+    <t>Les	méthodes	d'acquisition	des	données	seront	décrites	dans	les	protocoles	expérimentaux
+fournis	par	chacun	des	sites.	Les	acquisitions	ayant	été	souvent	non	coordonnées	entre	sites,	les
+jeux	de	données	sont	initialement	hétérogènes,	par	nature	et/	mode	de	gestion.
+Les	données	seront,	autant	que	possible,	rendues	interopérables	par	leur	traitement	avec	les
+outils	développés	dans	l'Infrastructure	de	Recherche	AnaEE	France.	La	chaîne	de	traitement	est
+basée	sur	l'annotation	sémantique	et	les	technologie	du	"linked	data".</t>
+  </si>
+  <si>
+    <t>Les	méta-données	seront	présentées	et	fournies	selon	les	standards	utilisés	par	les
+infrastructures	de	recherche	ICOS	et	AnaEE</t>
+  </si>
+  <si>
+    <t>&amp;Les	jeux	de	données	rendus	interopérables	par	la	chaîne	de	traitement	sémantique	sont
+accompagnés	de	métadonnées	:	1)	de	métadonnées	de	découverte	aux	standards	DCAT	(enrichi
+pour	compatibilité	avec	le	profil	DCAT	de	DATA	Terra)	et	ISO,	et	2)	de	métadonnées
+d'exploitation	issus	sur	la	modélisation	sémantique&amp;</t>
+  </si>
+  <si>
+    <t>DCAT	(Data	Catalog	Vocabulary)	:	https://rdamsc.bath.ac.uk/msc/m12
+ISO	19115	:	https://rdamsc.bath.ac.uk/msc/m22
+NetCDF	Attribute	Convention	for	Dataset	Discovery	:	https://rdamsc.bath.ac.uk/msc/m89</t>
+  </si>
+  <si>
+    <t>Les	jeux	de	données	produits	par	la	chaîne	de	traitement	sémantique	peuvent	bénéficier	de
+vérification	de	qualité	et	cohérence	basée	sur	des	contraintes	SHACL	applicables	aux	données
+produites	au	format	RDF.</t>
+  </si>
+  <si>
+    <t>Le	traitement	des	données	sera	effectué	par	chacun	des	groupes	de	recherche	responsable	des
+sites	expérimentaux	selon	les	méthodes	actuellement	appliquées	localement	et	décrites	dans	les
+protocoles	expérimentaux.
+La	mise	en	interopérabilité	des	jeux	de	données	sera	effectuée	avec	les	outils	développés	dans
+AnaEE-France.	La	chaîne	de	traitement	est	basée	sur	l'annotation	sémantique	et	les	technologie
+du	"linked	data".	
+Ce	traitement	est	aussi	celui	mis	en	oeuvre	dans	le	Projet	Ciblé	ALAMOD	de	FairCarboN	et	les	2
+opérations	s'effectueront	de	manière	coordonnée.</t>
+  </si>
+  <si>
+    <t>&amp;Ces	données	auront	un	haut	potentiel	de	réutilisation	pour	des	projets	futurs&amp;</t>
+  </si>
+  <si>
+    <t>&amp;Les	données	seront	partagées	selon	les	formats	actuellement	en	vigueur	dans	les	infrastructures
+de	recherche	ICOS	et	AnaEE	(CSV,	XLS,	TXT,	etc…&amp;</t>
+  </si>
+  <si>
+    <t>&amp;L'ensemble	de	ces	données	a	vocation	à	être	conservé	à	long-terme,	au	delà	de	la	durée	du
+projet	Drought	ForC	dans	les	entrepôts	de	données	du	Carbon	Portal	ICOS	et	l'entrepôt	national
+Recherche	Data	Gouv&amp;</t>
+  </si>
+  <si>
+    <t>L'expérience	MEDSOCLIM	est	commune	aux	sites	expérimentaux	méditerranéens	de	l'O3HP	et
+Puéchabon.	Cette	expérience	vise	à	manipuler	l'humidité	et	la	température	du	sol	sur	de	petites
+placettes	grâce	à	un	dispositif	d'exclusion	de	pluie	par	toit	amovible	et	de	chauffage	du	sol	sans
+contact.</t>
+  </si>
+  <si>
+    <t>Les	données	de	ce	produit	de	recherche	comprennent:
+Les	protocoles	et	matériels	utilisés	pour	réaliser	l'expérience
+Les	données	de	caractérisation	des	parcelles	et	du	sol	avant	le	démarrage	de	l'expérience
+Les	données	de	température	et	humidité	du	sol	avant	et	pendant	l'expérience</t>
+  </si>
+  <si>
+    <t>Expérience,	Exclusion	de	pluie,	Chauffage	du	sol</t>
+  </si>
+  <si>
+    <t>L'expérience	MEDSOCLIM	étant	nouvelle	et	réalisée	dans	le	cadre	du	projet	Drought	ForC,	il
+n'y	a	pas	de	données	pré-existantes	à	ré-utiliser</t>
+  </si>
+  <si>
+    <t>Les	protocoles	seront	rédigés	par	les	responsables	techniques	des	sites	de	Puéchabon	et
+O3HP.
+Les	données	de	caractérisation	du	sol	des	parcelles	seront	obtenues	par	échantillonage	et
+analyses	en	laboratoire	avant	le	démarrage	de	l'expérience
+Les	données	de	température	et	humidité	du	sol	dans	les	parcelles	expérimentales	seront
+acquise	par	des	capteurs	environnementaux	de	type	sondes	TDR	et	sondes	de
+température	(thermocouple,	PT100	ou	T107)	reliées	à	des	centrales	d'acquisition	avec	un
+pas	de	temps	de	30	min</t>
+  </si>
+  <si>
+    <t>&amp;standards Anaee&amp;</t>
+  </si>
+  <si>
+    <t>&amp;La	qualité	et	le	contrôle	des	données	seront	assurés	par	les	équipes	techniques	de	l'O3HP	et	de
+Puéchabon,	et	seront	réalisés	de	façon	similaire	aux	autres	données	collectées	sur	les	dispositifs
+expérimentaux	AnaEE	des	ces	sites&amp;</t>
+  </si>
+  <si>
+    <t>Les	données	brutes	seront	vérifiées	et	filtrées	grace	aux	logiciels	R	ou
+Excel,	puis	les	données	traitées	seront	enregistrées	en	format	XLS	et	CSV</t>
+  </si>
+  <si>
+    <t>xls ou csv</t>
+  </si>
+  <si>
+    <t>&amp;La	sécurité	de	ces	données	sera	sous	la	responsabilité	des	sites	expérimentaux	AnaEE	de
+l'O3HP	et	Puéchabon,	selon	les	usages	actuellement	en	vigueur	dans	ces	sites	expérimentaux&amp;</t>
+  </si>
+  <si>
+    <t>&amp;Les	données	nouvelles	sur	la	productivité	des	arbres	comprennent	toutes	les	mesures	qui	seront
+acquises	dans	le	cadre	du	WP2	du	projet	Drought	ForC&amp;</t>
+  </si>
+  <si>
+    <t>cquises	dans	le	cadre	du	WP2	du	projet	Drought	ForC,	à	savoir:
+des	mesures	de	dendrochronologie	sur	des	carottes	de	bois	prélevés	dans	les	troncs
+(largeur	de	cernes,	densité	du	bois,	ratio	isotopiques	en	13C	et	18O
+des	mesures	de	traits	foliaires	et	architecturaux	de	branches	(LMA,	13C	foliaire,
+croissance	primaire)
+des	mesures	d'allocation	et	de	croissance	souterraine	des	arbres	(biomasses	et
+croissances	racinaires,	croissances	de	hyphes	mycorhiziens)</t>
+  </si>
+  <si>
+    <t>Croissance,	Dendrochronologie,	Isotopes	C	et	O,	Architecture,	Racines,	Feuilles</t>
+  </si>
+  <si>
+    <t>Les	données	nouvelles	sur	la	productivité	des	arbres	seront	acquises	par	prélèvement
+d'échantillons	dans	le	différents	sites	expérimentaux	puis	analyse	de	ces	échantillons	en
+laboratoire:
+Des	carottes	de	bois	seront	prélevées	dans	les	troncs	de	certains	arbres	sélectionnés	dans
+chaque	site	et	traitement,	puis	ces	carottes	seront	analysées	par	une	ou	plusieurs
+plateformes	d'analyse	pour	mesurer	les	largeurs	de	cernes,	la	densité	du	bois,	et	les	ratios
+isotopiques	en	13C	et	18O
+Des	feuilles	seront	prélevées	à	différentes	dates	au	cours	du	projet	pour	des	mesures	de
+masse	surfacique	puis	le	ratio	isotopique	en	13C	sera	déterminé	par	une	plateforme
+d'analyse	isotopique
+Des	branches	seront	coupées	sur	certains	arbres	sélectionnés	dans	chaque	site	et
+traitements,	puis	ces	branches	seront	mesurées	au	laboratoire	pour	déterminer	un	certain
+nombre	de	traits	architecturaux	et	de	croissance	primaire	(nombre	de	ramifications,
+d'entre-noeuds,	de	feuilles,	etc...)
+Des	carottes	de	sol	seront	prélevées	dans	les	différents	sites	et	traitements	et	remplacées
+par	des	"in-growth	cores"	et	des	"hyphals	bags"	pour	mesurer	la	croissance	racinaire	et
+l'allocation	aux	hyphes	mycorhiziens.	Les	racines	et	les	hyphes	seront	ensuite	extraits	des
+carottes	et	mesurés	aux	laboratoires	INRAE	de	Bordeaux	(ISPA)	et	Nancy	(BEF).</t>
+  </si>
+  <si>
+    <t>Plateforme	SilvaTech	INRAE</t>
+  </si>
+  <si>
+    <t>&amp;La	qualité	scientifique	des	données	sera	assurée	par	un	nombre	d'échantillons	suffisant	pour
+être	représentatif	de	chacune	des	modalités	expérimentales,	par	des	analyses	centralisées	dans
+un	seul	laboratoire	(différent	selon	les	variables)	pour	l'ensemble	des	sites	concernés,	et	par	la
+comparaison	des	résultats	obtenus	avec	les	données	pré-existantes	pour	certains	des	sites	ou
+traitements&amp;</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>&amp;serveurs institutionnels&amp;</t>
+  </si>
+  <si>
+    <t>&amp;haut potentiel&amp;</t>
+  </si>
+  <si>
+    <t>xls, csv, txt</t>
+  </si>
+  <si>
+    <t>&amp;Les	données	nouvelles	sur	le	fonctionnement	du	sol	comprennent	toutes	les	mesures	qui	seront
+acquises	dans	le	cadre	du	WP3	du	projet	Drought	ForC&amp;</t>
+  </si>
+  <si>
+    <t>des	mesures	de	respiration	du	sol	dans	les	différents	sites	et	traitements
+des	mesures	d'emission	de	COV-B	par	les	sols	dans	les	traitements	expérimentaux	de
+chauffage	du	sol	et	sécheresse	à	l'O3HP	et	à	Puéchabon
+des	mesures	de	décomposition	de	la	litière	de	feuilles	dans	les	différents	sites	et
+traitements
+des	mesures	de	contenu	en	carbone	du	sol	dans	les	différents	horizons	superficiels	dans
+les	différents	sites	et	traitements
+des	inventaires	de	biodiveristé	de	la	faune	et	des	micro-organismes	du	sol	dans	certains
+sites	et	dispositifs	expérimentaux</t>
+  </si>
+  <si>
+    <t>Respiration	du	sol,	Décomposition	litière,	Activité	biologique	du	sol,	carbone	du	sol</t>
+  </si>
+  <si>
+    <t>Les	données	nouvelles	sur	le	fonctionnement	du	sol	seront	acquises	principalement	par	des
+mesures	et	expérimentations	sur	le	terrain,	mais	aussi	par	des	prélèvement	d'échantillons	dans
+le	différents	sites	expérimentaux	puis	analyse	de	ces	échantillons	en	laboratoire:
+Les	mesures	de	respiration	du	sol	seront	collectées	grâce	à	des	analyseurs	de	CO2
+portables	ou	fixes	qui	seront	installés	dans	le	différents	traitements	expérimentaux	des
+différents	sites	pour	mesurer	l'efflux	de	CO2	du	sol
+Les	mesures	d'émission	de	COV-B	seront	mesurés	grâce	à	des	campagnes	de	terrain	à
+l'O3HP	et	à	Puéchabon	avec	un	PTR-MS	mobile	ou	des	cartouches	de	prélèvements
+Les	mesures	de	décomposition	de	la	litière	de	feuilles	seront	réalisées	grâce	à	une
+expérience	in-situ	de	décomposition	sur	3	années	réalisée	par	la	méthode	des	litterbags
+avec	des	prélèvements	réguliers	tous	les	6	mois
+Les	mesures	de	contenu	en	carbone	du	sol	seront	réalisées	par	des	prélèvements
+d'échantillons	sur	le	terrain	qui	seront	ensuite	séchés	et	analysés	en	laboratoire
+Les	mesures	d'inventaire	de	biodiversité	de	faune	du	sol	ou	de	micro-organismes	seront
+réalisées	par	des	prélèvements	d'échantillons	de	sol	sur	le	terrain	qui	seront	ensuite
+analysés	en	laboratoire</t>
+  </si>
+  <si>
+    <t>experimentales</t>
+  </si>
+  <si>
+    <t>&amp;Les	données	nouvelles	sur	le	fonctionnement	du	sol	comprennent	toutes	les	mesures	qui	seront
+acquises	dans	le	cadre	du	WP4	du	projet	Drought	ForC&amp;</t>
+  </si>
+  <si>
+    <t>Nutriments,	Resorption,	Recyclage,	Sol</t>
+  </si>
+  <si>
+    <t>des	mesures	de	concentrations	en	nutriments	et	minéraux	dans	les	feuilles	vertes	des
+arbres	des	différents	sites	et	traitements
+des	mesures	de	concentrations	en	nutriments	et	minéraux	dans	les	feuilles	sénescentes
+des	arbres	des	différents	sites	et	traitements
+des	mesures	de	concentrations	en	nutriments	et	minéraux	dans	les	racines	fines	des
+arbres	des	différents	sites	et	traitements
+des	mesures	de	concentrations	en	nutriments	et	minéraux	dans	les	horizons
+holorganiques	du	sol	des	différents	sites	et	traitements
+des	mesures	de	cations	échangeables	et	capacité	d'échange	cationique	du	sol	des
+différents	sites	et	traitements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les	données	nouvelles	sur	le	statut	nutritif	des	arbres,	la	fertilité	des	sols	et	les	cycles
+biogéochimiques	seront	acquises	par	des	prélèvements	d'échantillons	dans	le	différents	sites
+expérimentaux	puis	analyses	de	ces	échantillons	en	laboratoire:
+Des	feuilles	vertes	seront	prélevées	à	différentes	dates	dans	chacun	des	sites	et	des
+traitements	puis	analysées	par	une	ou	plusieurs	plateformes	d'analyse	pour	mesurer	les
+concentrations	en	N,P,K	et	autres	éléments	minéraux
+Des	feuilles	sénescentes	seront	prélevées	à	différentes	dates	dans	chacun	des	sites	et
+traitements	puis	analysées	par	une	ou	des	plateformes	d'analyse	pour	mesurer	les
+concentrations	en	N,P,K	et	autres	éléments	minéraux
+Des	racines	fines	seront	prélevées	à	différentes	dates	dans	chacun	des	sites	et	traitements
+puis	analysées	par	une	ou	des	plateformes	d'analyse	pour	mesurer	les	concentrations	en
+N,P,K	et	autres	éléments	minéraux
+Du	sol	de	différents	horizons	sera	prélevé	dans	les	différents	sites	et	traitements	et
+analysés	par	une	ou	des	plateformes	d'analyse	pour	mesurer	les	concentrations	en	N,P,K
+et	autres	éléments	minéraux	</t>
+  </si>
+  <si>
+    <t>11 Go</t>
+  </si>
+  <si>
+    <t>Données	environnementales	et	écophysiologiques	dont	la	collecte	a	débuté	avant	le	projet
+Drought	ForC	et	a	été	réalisée	par	les	chercheurs	et	personnels	techniques	des	8	sites
+expérimentaux	du	projet.	Ces	données	qui	sont	en	partie	similaires	à	celles	décrites	dans	la
+section	"Données	existantes"	sont	spécifiquement	sélectionnées	par	les	chercheurs	responsables
+de	réaliser	les	simulations	afin	de	paramétrer	et/ou	calibrer	les	modèles	et	de	servir	de	forçage
+pour	les	simulations</t>
+  </si>
+  <si>
+    <t>Ces	données	concernent:
+les	variables	météorologiques
+le	contenu	en	eau	du	sol
+les	flux	de	carbone,	eau	et	énergie
+la	croissance	et	la	mortalité	des	arbres
+les	traits	morphologiques	et	écophysiologiques	des	arbres
+la	caractérisation	physico-chimique	du	sol
+les	analyses	chimiques	des	nutriments	dans	le	différents	compartiments	du	sol	et	des
+arbres</t>
+  </si>
+  <si>
+    <t>Les	données	de	ce	produit	de	recherche	sont	principalement	des	données	existantes	qui	seront
+ré-utilisées	mais	devront	être	préparées	et	mises	en	forme	de	façon	spécifique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A	partir	des	données	existantes	pour	les	différents	sites	et	traitements	expérimentaux	mais
+couvrant	des	périodes	différentes,	et	acquises	à	des	grains	spatiaux	et	temporels	différents,	le
+travail	de	production	de	ces	données	consistera	à	les	sélectionner,	filtrer,	gapfiler	et	mettre	en
+forme	de	façon	à	ce	qu'elles	puissent	facilement	servir	pour	le	forçage	et	le	paramétrage	des
+différents	modèles	impliqués	dans	le	projet	Drought	ForC	et	qui	ont	chacun	aussi	leurs
+spécifications	en	terme	de	pas	de	temps,	de	grain	spatial	et	paramètres	d'entrée.
+La	méthode	de	production	de	ces	fichiers	de	données	est	à	définir	par	les	chercheurs	impliques
+dans	le	WP5	de	Drought	ForC	et	ceux	impliqués	dans	le	projet	ciblé	ALAMOD	du	PEPR
+FairCarboN.	</t>
+  </si>
+  <si>
+    <t>&amp;Les	méta-données	seront	présentées	et	fournies	selon	les	choisis	par	le	projet	ciblé	ALAMOD	du
+PEPR	FairCarboN&amp;</t>
+  </si>
+  <si>
+    <t>&amp;Les	procédures	de	contrôle	qualité	des	données	seront	celles	existantes	actuellement	dans	les
+infrastructures	de	recherche	ICOS	et	AnaEE.	La	qualité	des	données	sera	aussi	vérifiée	par	la
+cohérence	avec	la	littérature	scientifique	et	les	paramètres	déjà	utilisés	par	les	différents
+modèles&amp;</t>
+  </si>
+  <si>
+    <t>&amp;Les	données	seront	stockées	de	façon	centralisée	par	les	responsables	du	WP5	de	Drought
+ForC,	par	les	responsables	des	données	du	projet	ciblé	ALAMOD	de	FairCarboN,	et	par	les
+groupes	de	modélisateurs	qui	seront	chargés	de	réaliser	les	simulations&amp;</t>
+  </si>
+  <si>
+    <t>&amp;Les	données	seront	partagées	selon	les	formats	actuellement	utilisés	par	les	différents	groupes
+de	recherche	impliqués	(CSV,	XLS,	TXT,	NetCDF),	et	rendues	disponibles	conformément	aux
+pratiques	mises	en	oeuvres	dans	le	projet	ciblé	ALAMOD	du	PEPR	FairCarboN&amp;</t>
+  </si>
+  <si>
+    <t>xls, csv, txt, NetCDF</t>
+  </si>
+  <si>
+    <t>Simulations	numériques	en	climat	présent	et	en	climat	futur	réalisées	avec	les	différents
+modèles	mécanistes	impliqués	dans	le	projet	Drought	ForC</t>
+  </si>
+  <si>
+    <t>Les	modèles	actuellement	identifiés	pour	réaliser	ces	simulations	sont:
+ForCEEPS
+GO+
+MAESPA
+MuSICA
+NoTG
+ORCHIDEE
+PhenoFit
+SALEM
+SAMSARA
+SIERRA
+SUREAU
+TROLL
+YASSO</t>
+  </si>
+  <si>
+    <t>Modélisation	mécaniste,	Simulations,	Climat	futur</t>
+  </si>
+  <si>
+    <t>simulation</t>
+  </si>
+  <si>
+    <t>&amp;Les	nouvelles	données	seront	produites	par	des	simulations	numériques	en	utilisant	les
+différents	modèles	inclus	dans	cette	tache&amp;</t>
+  </si>
+  <si>
+    <t>&amp;Les	modèles	utilisés	sont	tous	déjà	publiés	et	décrits.	Des	fiches-résumé	des	besoins	de	chaque
+modèle	ont	été	rédigées	et	pourront	accompagner	les	jeux	de	données	simulées	lors	de	leur.s
+publication.s&amp;</t>
+  </si>
+  <si>
+    <t>1 To</t>
+  </si>
+  <si>
+    <t>Le	modèle	CASTANEA-MAESPA-CNPK	sera	un	nouveau	modèle	informatique	basé	sur	
+les	processus	et	destiné	à	coupler	les	cycles	de	l'eau,	du	carbone	eet	des	minéraux	
+N,	P	et	K	dans	les	peuplements	forestiers.	Ce	modèle	sera	développé	sur	la	base	de	
+travaux	existants	pour	le	potassium	et	peremetra	une	meilleure	représentation	des	
+processus	physiologiques	(fonctionnement	hydraulique	des	arbres	grâce	au	
+couplage	avec	le	modèle	SurEau)	et	des	processus	biogéochimiques	dans	le	sol.	Le	
+modèle	sera	paramétré	et	validé	en	utilisant	les	données	du	site	expérimental	de	
+Itatinga	(Brésil)	et	un	ensemble	de	plantations	d'eucalyptus	au	Brésil	avec	différents	
+essais	de	fertilisation.</t>
+  </si>
+  <si>
+    <t>Cycles	biogéochimiques,	Ecophysiologie	de	l'arbre,	Modèle	basé	sur	les	processus,	Plantations
+fertilisées</t>
+  </si>
+  <si>
+    <t>Le	développement	du	modèle	CASTANEA-MAESPA-CNPK	réutilisera	des	codes	issus	des
+modèles	CASTANEA	et	MAESPA.
+La	paramétrisation,	le	forçage	et	la	validation	du	modèle	CASTANEA-MAESPA-CNPK	sera	fait
+en	utilisant	des	données	existantes	issues	de	Itatinga	(voir	section	"données	existantes")	et
+d'autres	données	issues	de	plantations	et	essais	de	fertilisation	au	Brésil.</t>
+  </si>
+  <si>
+    <t>&amp;Le	nouveau	modèle	sera	développé	et	codé	à	partir	des	modèles	existants	CASTANEA,	MAESPA
+et	SurEau	et	de	recherches	menées	par	les	chercheurs	impliqués	dans	cette	tache&amp;</t>
+  </si>
+  <si>
+    <t>modèle</t>
+  </si>
+  <si>
+    <t>&amp;The PEACE project will produce new data from field studies (seasonal and annual monitoring), 
+laboratory analysis, remote sensing analysis as well as modeling. 
+Existing  published  data  from  team  members  of  studied  complementary  sites  will  be 
+incorporated. Reanalysis of permafrost core or soil sample will produce new data&amp;</t>
+  </si>
+  <si>
+    <t>The  PEACE  project  will  produce  new  data  about  the  permafrost/soil  characteristics, 
+hydrosystem biogeochemistry, greenhouse gases flux and microbial communities : 
+Database  of  biogeochemical  characteristics  of  permafrost/soils  and  ecosystems 
+(structure, mineralogy, OM content) 
+Database  of  particulate  organic,  dissolved  inorganic  and  organic  elements  from 
+groundwater and surface water (concentration mg/L) 
+Database of 14C content of POC, DOC, CH4 and CO2 from diverse water bodies 
+Database of climatic parameters (temperature, precipitation, solar radiation, …) from 
+the weather station 
+Database of environmental and climatic parameters (temperature, precipitation, solar 
+radiation, …) from the local-community observatories 
+Greenhouse gases concentration (µmol/L) from surface waters and permafrost 
+Metabarcoding-based  description  of  the  structure  of  250  communities  and  of  their 
+active fraction (raw sequences) 
+15 metagenomes informing the metabolic potential of microbial communities in crucial 
+samples.</t>
+  </si>
+  <si>
+    <t>&amp; open  access  data  service  ESPRI  at  Institut  Pierre  Simon  Laplace  (Paris, 
+https://mesocentre.ipsl.fr/) and Institutional open source data repository systems of Service de 
+données de l'Observatoire Midi-Pyrénées (SEDOO, Toulouse, https://www.sedoo.fr/). Several 
+online tools will be used to help to create and daily manage the datasets (DMP OPIDoR and 
+DMP Online). &amp;</t>
+  </si>
+  <si>
+    <t>Environmental dataset (soil, water, gas) will be described with the support of ESPRI-IPSL, 
+SEDOO-OMP  which  is  part  of  the  French  national  DATAterra  infrastructure.  The  PEACE 
+project will contribute to the data hub specialized in land surface (THEIA). The Data Terra 
+research infrastructure insureq a long-term preservation of data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+Microbial datasets along with sample metadata will be referenced in the international Global 
+Biodiversity Information Facility (GBIF). There is a dedicated online portal for microbial dataset 
+(Pola3r)  dedicated  to  facilitate  the  discovery,  access  and  analysis  of  molecular  microbial 
+diversity  (meta)data  by  Antarctic,  Arctic  and  Alpine  researchers.  Standardized  information 
+about sequence data (Yilmaz et al., 2011) will be reported together with environmental data, 
+3 
+formatted as defined by the Genomic Standards Consortium (Field et al., 2011) and published 
+in the DRYAD platform (fully available under a CC0 1.0 license, with DOI)</t>
+  </si>
+  <si>
+    <t>dryad et gbif</t>
+  </si>
+  <si>
+    <t>&amp; 
+The  collaboration  with  ESPRI-IPSL,  SEDOO-OMP  will  ensure  a  correct  description  of  the 
+metadata, keywords, and standard format thanks to their expertise &amp;</t>
+  </si>
+  <si>
+    <t>Preliminary  data  acquired  during  field  studies  will  be  made  available  through  ftp  and  a 
+restricted workspace from each Institution at first and then with a website designed specifically 
+for the project. This will ensure easy data sharing between consortium members and partners.</t>
+  </si>
+  <si>
+    <t>Publications  of  data  papers  on  original  research  data  in  international  and  interdisciplinary 
+journals  such  as  Earth  System  Science  Data  (Copernicus),  Freshwater  Metadata  Journal 
+(Elsevier) or  Ecological Research (Springer). Inside the paper, the data set as well as the 
+context is described to highlight the value. The project final report will include information on 
+the data and metadata archives with links to the open source datasets as well as our catalog</t>
+  </si>
+  <si>
+    <t>Data sets will be accessible through the web interface (metacatalog) of the website of ESPRI-
+IPSL, SEDOO-OMP as well as from the French national DATAterra infrastructure. The ESPRI-
+IPSL recently developed a web GIS interface of the metacalog to facilitate the selection and 
+download of data from a web browser through spatial and temporal criteria</t>
+  </si>
+  <si>
+    <t>Antoine Séjourné, Maialen Barret</t>
+  </si>
+  <si>
+    <t>The  recruitment  of  two  engineers  is  necessary  for  the 
+standardization of the data and the construction of the database</t>
   </si>
 </sst>
 </file>
@@ -18538,7 +19113,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="71" spans="1:102" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>41</v>
       </c>
@@ -18555,7 +19130,7 @@
         <v>30</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>219</v>
+        <v>928</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>321</v>
@@ -18592,9 +19167,7 @@
       <c r="U71" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="V71" s="1" t="s">
-        <v>219</v>
-      </c>
+      <c r="V71" s="1"/>
       <c r="W71" s="1" t="s">
         <v>249</v>
       </c>
@@ -18621,18 +19194,32 @@
       <c r="AF71" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="AG71" s="1"/>
-      <c r="AH71" s="1"/>
+      <c r="AG71" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AH71" s="1" t="s">
+        <v>929</v>
+      </c>
       <c r="AI71" s="1"/>
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
-      <c r="AL71" s="1"/>
-      <c r="AM71" s="1"/>
+      <c r="AL71" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="AM71" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="AN71" s="1"/>
-      <c r="AO71" s="1"/>
-      <c r="AP71" s="1"/>
+      <c r="AO71" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AP71" s="1" t="s">
+        <v>931</v>
+      </c>
       <c r="AQ71" s="1"/>
-      <c r="AR71" s="1"/>
+      <c r="AR71" s="1" t="s">
+        <v>932</v>
+      </c>
       <c r="AS71" s="1"/>
       <c r="AT71" s="1"/>
       <c r="AU71" s="1"/>
@@ -18640,7 +19227,9 @@
       <c r="AW71" s="1"/>
       <c r="AX71" s="1"/>
       <c r="AY71" s="1"/>
-      <c r="AZ71" s="1"/>
+      <c r="AZ71" s="1" t="s">
+        <v>933</v>
+      </c>
       <c r="BA71" s="1"/>
       <c r="BB71" s="1"/>
       <c r="BC71" s="1"/>
@@ -18648,17 +19237,23 @@
       <c r="BE71" s="1"/>
       <c r="BF71" s="1"/>
       <c r="BG71" s="1"/>
-      <c r="BH71" s="1"/>
+      <c r="BH71" s="1" t="s">
+        <v>934</v>
+      </c>
       <c r="BI71" s="1"/>
       <c r="BJ71" s="1"/>
       <c r="BK71" s="1"/>
       <c r="BL71" s="1"/>
       <c r="BM71" s="1"/>
       <c r="BN71" s="1"/>
-      <c r="BO71" s="1"/>
+      <c r="BO71" s="1" t="s">
+        <v>935</v>
+      </c>
       <c r="BP71" s="1"/>
       <c r="BQ71" s="1"/>
-      <c r="BR71" s="1"/>
+      <c r="BR71" s="1" t="s">
+        <v>936</v>
+      </c>
       <c r="BS71" s="1"/>
       <c r="BT71" s="1"/>
       <c r="BU71" s="1"/>
@@ -18668,17 +19263,25 @@
       <c r="BY71" s="1"/>
       <c r="BZ71" s="1"/>
       <c r="CA71" s="1"/>
-      <c r="CB71" s="1"/>
-      <c r="CC71" s="1"/>
+      <c r="CB71" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="CC71" s="1" t="s">
+        <v>937</v>
+      </c>
       <c r="CD71" s="1"/>
       <c r="CE71" s="1"/>
-      <c r="CF71" s="1"/>
+      <c r="CF71" s="1" t="s">
+        <v>939</v>
+      </c>
       <c r="CG71" s="1"/>
       <c r="CH71" s="1"/>
       <c r="CI71" s="1"/>
       <c r="CJ71" s="1"/>
       <c r="CK71" s="1"/>
-      <c r="CL71" s="1"/>
+      <c r="CL71" s="1" t="s">
+        <v>940</v>
+      </c>
       <c r="CM71" s="1"/>
       <c r="CN71" s="1"/>
       <c r="CO71" s="1"/>
@@ -18690,9 +19293,11 @@
       <c r="CU71" s="1"/>
       <c r="CV71" s="1"/>
       <c r="CW71" s="1"/>
-      <c r="CX71" s="1"/>
+      <c r="CX71" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="72" spans="1:102" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>41</v>
       </c>
@@ -18709,7 +19314,7 @@
         <v>30</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>219</v>
+        <v>928</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>321</v>
@@ -18775,18 +19380,38 @@
       <c r="AF72" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AG72" s="1"/>
-      <c r="AH72" s="1"/>
-      <c r="AI72" s="1"/>
-      <c r="AJ72" s="1"/>
-      <c r="AK72" s="1"/>
-      <c r="AL72" s="1"/>
-      <c r="AM72" s="1"/>
+      <c r="AG72" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AH72" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="AI72" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="AJ72" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="AK72" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="AL72" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="AM72" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="AN72" s="1"/>
-      <c r="AO72" s="1"/>
-      <c r="AP72" s="1"/>
+      <c r="AO72" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AP72" s="1" t="s">
+        <v>945</v>
+      </c>
       <c r="AQ72" s="1"/>
-      <c r="AR72" s="1"/>
+      <c r="AR72" s="1" t="s">
+        <v>946</v>
+      </c>
       <c r="AS72" s="1"/>
       <c r="AT72" s="1"/>
       <c r="AU72" s="1"/>
@@ -18794,49 +19419,73 @@
       <c r="AW72" s="1"/>
       <c r="AX72" s="1"/>
       <c r="AY72" s="1"/>
-      <c r="AZ72" s="1"/>
+      <c r="AZ72" s="1" t="s">
+        <v>948</v>
+      </c>
       <c r="BA72" s="1"/>
       <c r="BB72" s="1"/>
       <c r="BC72" s="1"/>
       <c r="BD72" s="1"/>
-      <c r="BE72" s="1"/>
+      <c r="BE72" s="1" t="s">
+        <v>947</v>
+      </c>
       <c r="BF72" s="1"/>
       <c r="BG72" s="1"/>
-      <c r="BH72" s="1"/>
+      <c r="BH72" s="1" t="s">
+        <v>949</v>
+      </c>
       <c r="BI72" s="1"/>
-      <c r="BJ72" s="1"/>
-      <c r="BK72" s="1"/>
+      <c r="BJ72" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="BK72" s="1" t="s">
+        <v>950</v>
+      </c>
       <c r="BL72" s="1"/>
       <c r="BM72" s="1"/>
       <c r="BN72" s="1"/>
-      <c r="BO72" s="1"/>
+      <c r="BO72" s="1" t="s">
+        <v>952</v>
+      </c>
       <c r="BP72" s="1"/>
       <c r="BQ72" s="1"/>
       <c r="BR72" s="1"/>
       <c r="BS72" s="1"/>
       <c r="BT72" s="1"/>
       <c r="BU72" s="1"/>
-      <c r="BV72" s="1"/>
+      <c r="BV72" s="1" t="s">
+        <v>953</v>
+      </c>
       <c r="BW72" s="1"/>
       <c r="BX72" s="1"/>
       <c r="BY72" s="1"/>
       <c r="BZ72" s="1"/>
       <c r="CA72" s="1"/>
       <c r="CB72" s="1"/>
-      <c r="CC72" s="1"/>
+      <c r="CC72" s="1" t="s">
+        <v>350</v>
+      </c>
       <c r="CD72" s="1"/>
       <c r="CE72" s="1"/>
       <c r="CF72" s="1"/>
       <c r="CG72" s="1"/>
       <c r="CH72" s="1"/>
-      <c r="CI72" s="1"/>
-      <c r="CJ72" s="1"/>
+      <c r="CI72" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="CJ72" s="1" t="s">
+        <v>903</v>
+      </c>
       <c r="CK72" s="1"/>
-      <c r="CL72" s="1"/>
+      <c r="CL72" s="1" t="s">
+        <v>955</v>
+      </c>
       <c r="CM72" s="1"/>
       <c r="CN72" s="1"/>
       <c r="CO72" s="1"/>
-      <c r="CP72" s="1"/>
+      <c r="CP72" s="1" t="s">
+        <v>956</v>
+      </c>
       <c r="CQ72" s="1"/>
       <c r="CR72" s="1"/>
       <c r="CS72" s="1"/>
@@ -18844,9 +19493,11 @@
       <c r="CU72" s="1"/>
       <c r="CV72" s="1"/>
       <c r="CW72" s="1"/>
-      <c r="CX72" s="1"/>
+      <c r="CX72" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="73" spans="1:102" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>41</v>
       </c>
@@ -18863,7 +19514,7 @@
         <v>30</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>219</v>
+        <v>928</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>321</v>
@@ -18929,27 +19580,59 @@
       <c r="AF73" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AG73" s="1"/>
-      <c r="AH73" s="1"/>
-      <c r="AI73" s="1"/>
+      <c r="AG73" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AH73" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="AI73" s="1" t="s">
+        <v>365</v>
+      </c>
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
-      <c r="AL73" s="1"/>
+      <c r="AL73" s="1" t="s">
+        <v>959</v>
+      </c>
       <c r="AM73" s="1"/>
       <c r="AN73" s="1"/>
-      <c r="AO73" s="1"/>
-      <c r="AP73" s="1"/>
-      <c r="AQ73" s="1"/>
-      <c r="AR73" s="1"/>
-      <c r="AS73" s="1"/>
-      <c r="AT73" s="1"/>
-      <c r="AU73" s="1"/>
-      <c r="AV73" s="1"/>
-      <c r="AW73" s="1"/>
-      <c r="AX73" s="1"/>
+      <c r="AO73" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AP73" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="AQ73" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="AR73" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="AS73" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="AT73" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="AU73" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="AV73" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="AW73" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="AX73" s="1" t="s">
+        <v>366</v>
+      </c>
       <c r="AY73" s="1"/>
-      <c r="AZ73" s="1"/>
-      <c r="BA73" s="1"/>
+      <c r="AZ73" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="BA73" s="1" t="s">
+        <v>958</v>
+      </c>
       <c r="BB73" s="1"/>
       <c r="BC73" s="1"/>
       <c r="BD73" s="1"/>
@@ -18958,35 +19641,49 @@
       <c r="BG73" s="1"/>
       <c r="BH73" s="1"/>
       <c r="BI73" s="1"/>
-      <c r="BJ73" s="1"/>
+      <c r="BJ73" s="1" t="s">
+        <v>962</v>
+      </c>
       <c r="BK73" s="1"/>
       <c r="BL73" s="1"/>
       <c r="BM73" s="1"/>
       <c r="BN73" s="1"/>
-      <c r="BO73" s="1"/>
+      <c r="BO73" s="1" t="s">
+        <v>963</v>
+      </c>
       <c r="BP73" s="1"/>
       <c r="BQ73" s="1"/>
       <c r="BR73" s="1"/>
       <c r="BS73" s="1"/>
       <c r="BT73" s="1"/>
       <c r="BU73" s="1"/>
-      <c r="BV73" s="1"/>
+      <c r="BV73" s="1" t="s">
+        <v>964</v>
+      </c>
       <c r="BW73" s="1"/>
       <c r="BX73" s="1"/>
       <c r="BY73" s="1"/>
       <c r="BZ73" s="1"/>
       <c r="CA73" s="1"/>
-      <c r="CB73" s="1"/>
+      <c r="CB73" s="1" t="s">
+        <v>919</v>
+      </c>
       <c r="CC73" s="1"/>
       <c r="CD73" s="1"/>
       <c r="CE73" s="1"/>
-      <c r="CF73" s="1"/>
+      <c r="CF73" s="1" t="s">
+        <v>966</v>
+      </c>
       <c r="CG73" s="1"/>
       <c r="CH73" s="1"/>
       <c r="CI73" s="1"/>
-      <c r="CJ73" s="1"/>
+      <c r="CJ73" s="1" t="s">
+        <v>903</v>
+      </c>
       <c r="CK73" s="1"/>
-      <c r="CL73" s="1"/>
+      <c r="CL73" s="1" t="s">
+        <v>965</v>
+      </c>
       <c r="CM73" s="1"/>
       <c r="CN73" s="1"/>
       <c r="CO73" s="1"/>
@@ -18998,9 +19695,11 @@
       <c r="CU73" s="1"/>
       <c r="CV73" s="1"/>
       <c r="CW73" s="1"/>
-      <c r="CX73" s="1"/>
+      <c r="CX73" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="74" spans="1:102" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>41</v>
       </c>
@@ -19017,7 +19716,7 @@
         <v>30</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>219</v>
+        <v>928</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>321</v>
@@ -19083,15 +19782,25 @@
       <c r="AF74" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AG74" s="1"/>
-      <c r="AH74" s="1"/>
-      <c r="AI74" s="1"/>
+      <c r="AG74" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AH74" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="AI74" s="1" t="s">
+        <v>372</v>
+      </c>
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
-      <c r="AL74" s="1"/>
+      <c r="AL74" s="1" t="s">
+        <v>969</v>
+      </c>
       <c r="AM74" s="1"/>
       <c r="AN74" s="1"/>
-      <c r="AO74" s="1"/>
+      <c r="AO74" s="1" t="s">
+        <v>396</v>
+      </c>
       <c r="AP74" s="1"/>
       <c r="AQ74" s="1"/>
       <c r="AR74" s="1"/>
@@ -19101,12 +19810,20 @@
       <c r="AV74" s="1"/>
       <c r="AW74" s="1"/>
       <c r="AX74" s="1"/>
-      <c r="AY74" s="1"/>
-      <c r="AZ74" s="1"/>
-      <c r="BA74" s="1"/>
+      <c r="AY74" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="AZ74" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="BA74" s="1" t="s">
+        <v>981</v>
+      </c>
       <c r="BB74" s="1"/>
       <c r="BC74" s="1"/>
-      <c r="BD74" s="1"/>
+      <c r="BD74" s="1" t="s">
+        <v>971</v>
+      </c>
       <c r="BE74" s="1"/>
       <c r="BF74" s="1"/>
       <c r="BG74" s="1"/>
@@ -19114,10 +19831,14 @@
       <c r="BI74" s="1"/>
       <c r="BJ74" s="1"/>
       <c r="BK74" s="1"/>
-      <c r="BL74" s="1"/>
+      <c r="BL74" s="1" t="s">
+        <v>973</v>
+      </c>
       <c r="BM74" s="1"/>
       <c r="BN74" s="1"/>
-      <c r="BO74" s="1"/>
+      <c r="BO74" s="1" t="s">
+        <v>972</v>
+      </c>
       <c r="BP74" s="1"/>
       <c r="BQ74" s="1"/>
       <c r="BR74" s="1"/>
@@ -19130,17 +19851,27 @@
       <c r="BY74" s="1"/>
       <c r="BZ74" s="1"/>
       <c r="CA74" s="1"/>
-      <c r="CB74" s="1"/>
-      <c r="CC74" s="1"/>
+      <c r="CB74" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="CC74" s="1" t="s">
+        <v>974</v>
+      </c>
       <c r="CD74" s="1"/>
       <c r="CE74" s="1"/>
       <c r="CF74" s="1"/>
       <c r="CG74" s="1"/>
       <c r="CH74" s="1"/>
-      <c r="CI74" s="1"/>
-      <c r="CJ74" s="1"/>
+      <c r="CI74" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="CJ74" s="1" t="s">
+        <v>903</v>
+      </c>
       <c r="CK74" s="1"/>
-      <c r="CL74" s="1"/>
+      <c r="CL74" s="1" t="s">
+        <v>976</v>
+      </c>
       <c r="CM74" s="1"/>
       <c r="CN74" s="1"/>
       <c r="CO74" s="1"/>
@@ -19152,9 +19883,11 @@
       <c r="CU74" s="1"/>
       <c r="CV74" s="1"/>
       <c r="CW74" s="1"/>
-      <c r="CX74" s="1"/>
+      <c r="CX74" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="75" spans="1:102" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>41</v>
       </c>
@@ -19171,7 +19904,7 @@
         <v>30</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>219</v>
+        <v>928</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>321</v>
@@ -19237,15 +19970,25 @@
       <c r="AF75" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AG75" s="1"/>
-      <c r="AH75" s="1"/>
-      <c r="AI75" s="1"/>
+      <c r="AG75" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AH75" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="AI75" s="1" t="s">
+        <v>352</v>
+      </c>
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
-      <c r="AL75" s="1"/>
+      <c r="AL75" s="1" t="s">
+        <v>979</v>
+      </c>
       <c r="AM75" s="1"/>
       <c r="AN75" s="1"/>
-      <c r="AO75" s="1"/>
+      <c r="AO75" s="1" t="s">
+        <v>396</v>
+      </c>
       <c r="AP75" s="1"/>
       <c r="AQ75" s="1"/>
       <c r="AR75" s="1"/>
@@ -19255,9 +19998,15 @@
       <c r="AV75" s="1"/>
       <c r="AW75" s="1"/>
       <c r="AX75" s="1"/>
-      <c r="AY75" s="1"/>
-      <c r="AZ75" s="1"/>
-      <c r="BA75" s="1"/>
+      <c r="AY75" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="AZ75" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="BA75" s="1" t="s">
+        <v>981</v>
+      </c>
       <c r="BB75" s="1"/>
       <c r="BC75" s="1"/>
       <c r="BD75" s="1"/>
@@ -19271,7 +20020,9 @@
       <c r="BL75" s="1"/>
       <c r="BM75" s="1"/>
       <c r="BN75" s="1"/>
-      <c r="BO75" s="1"/>
+      <c r="BO75" s="1" t="s">
+        <v>972</v>
+      </c>
       <c r="BP75" s="1"/>
       <c r="BQ75" s="1"/>
       <c r="BR75" s="1"/>
@@ -19284,17 +20035,25 @@
       <c r="BY75" s="1"/>
       <c r="BZ75" s="1"/>
       <c r="CA75" s="1"/>
-      <c r="CB75" s="1"/>
+      <c r="CB75" s="1" t="s">
+        <v>919</v>
+      </c>
       <c r="CC75" s="1"/>
       <c r="CD75" s="1"/>
       <c r="CE75" s="1"/>
       <c r="CF75" s="1"/>
       <c r="CG75" s="1"/>
       <c r="CH75" s="1"/>
-      <c r="CI75" s="1"/>
-      <c r="CJ75" s="1"/>
+      <c r="CI75" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="CJ75" s="1" t="s">
+        <v>903</v>
+      </c>
       <c r="CK75" s="1"/>
-      <c r="CL75" s="1"/>
+      <c r="CL75" s="1" t="s">
+        <v>976</v>
+      </c>
       <c r="CM75" s="1"/>
       <c r="CN75" s="1"/>
       <c r="CO75" s="1"/>
@@ -19306,9 +20065,11 @@
       <c r="CU75" s="1"/>
       <c r="CV75" s="1"/>
       <c r="CW75" s="1"/>
-      <c r="CX75" s="1"/>
+      <c r="CX75" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="76" spans="1:102" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>41</v>
       </c>
@@ -19325,7 +20086,7 @@
         <v>30</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>219</v>
+        <v>928</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>321</v>
@@ -19391,15 +20152,25 @@
       <c r="AF76" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AG76" s="1"/>
-      <c r="AH76" s="1"/>
-      <c r="AI76" s="1"/>
+      <c r="AG76" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AH76" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="AI76" s="1" t="s">
+        <v>382</v>
+      </c>
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
-      <c r="AL76" s="1"/>
+      <c r="AL76" s="1" t="s">
+        <v>983</v>
+      </c>
       <c r="AM76" s="1"/>
       <c r="AN76" s="1"/>
-      <c r="AO76" s="1"/>
+      <c r="AO76" s="1" t="s">
+        <v>396</v>
+      </c>
       <c r="AP76" s="1"/>
       <c r="AQ76" s="1"/>
       <c r="AR76" s="1"/>
@@ -19409,9 +20180,15 @@
       <c r="AV76" s="1"/>
       <c r="AW76" s="1"/>
       <c r="AX76" s="1"/>
-      <c r="AY76" s="1"/>
-      <c r="AZ76" s="1"/>
-      <c r="BA76" s="1"/>
+      <c r="AY76" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="AZ76" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="BA76" s="1" t="s">
+        <v>981</v>
+      </c>
       <c r="BB76" s="1"/>
       <c r="BC76" s="1"/>
       <c r="BD76" s="1"/>
@@ -19425,7 +20202,9 @@
       <c r="BL76" s="1"/>
       <c r="BM76" s="1"/>
       <c r="BN76" s="1"/>
-      <c r="BO76" s="1"/>
+      <c r="BO76" s="1" t="s">
+        <v>972</v>
+      </c>
       <c r="BP76" s="1"/>
       <c r="BQ76" s="1"/>
       <c r="BR76" s="1"/>
@@ -19438,17 +20217,25 @@
       <c r="BY76" s="1"/>
       <c r="BZ76" s="1"/>
       <c r="CA76" s="1"/>
-      <c r="CB76" s="1"/>
+      <c r="CB76" s="1" t="s">
+        <v>986</v>
+      </c>
       <c r="CC76" s="1"/>
       <c r="CD76" s="1"/>
       <c r="CE76" s="1"/>
       <c r="CF76" s="1"/>
       <c r="CG76" s="1"/>
       <c r="CH76" s="1"/>
-      <c r="CI76" s="1"/>
-      <c r="CJ76" s="1"/>
+      <c r="CI76" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="CJ76" s="1" t="s">
+        <v>903</v>
+      </c>
       <c r="CK76" s="1"/>
-      <c r="CL76" s="1"/>
+      <c r="CL76" s="1" t="s">
+        <v>976</v>
+      </c>
       <c r="CM76" s="1"/>
       <c r="CN76" s="1"/>
       <c r="CO76" s="1"/>
@@ -19460,9 +20247,11 @@
       <c r="CU76" s="1"/>
       <c r="CV76" s="1"/>
       <c r="CW76" s="1"/>
-      <c r="CX76" s="1"/>
+      <c r="CX76" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="77" spans="1:102" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>41</v>
       </c>
@@ -19479,7 +20268,7 @@
         <v>30</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>219</v>
+        <v>928</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>321</v>
@@ -19545,17 +20334,29 @@
       <c r="AF77" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AG77" s="1"/>
-      <c r="AH77" s="1"/>
-      <c r="AI77" s="1"/>
+      <c r="AG77" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AH77" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="AI77" s="1" t="s">
+        <v>391</v>
+      </c>
       <c r="AJ77" s="1"/>
       <c r="AK77" s="1"/>
       <c r="AL77" s="1"/>
       <c r="AM77" s="1"/>
       <c r="AN77" s="1"/>
-      <c r="AO77" s="1"/>
-      <c r="AP77" s="1"/>
-      <c r="AQ77" s="1"/>
+      <c r="AO77" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AP77" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="AQ77" s="1" t="s">
+        <v>988</v>
+      </c>
       <c r="AR77" s="1"/>
       <c r="AS77" s="1"/>
       <c r="AT77" s="1"/>
@@ -19564,8 +20365,12 @@
       <c r="AW77" s="1"/>
       <c r="AX77" s="1"/>
       <c r="AY77" s="1"/>
-      <c r="AZ77" s="1"/>
-      <c r="BA77" s="1"/>
+      <c r="AZ77" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="BA77" s="1" t="s">
+        <v>981</v>
+      </c>
       <c r="BB77" s="1"/>
       <c r="BC77" s="1"/>
       <c r="BD77" s="1"/>
@@ -19575,11 +20380,15 @@
       <c r="BH77" s="1"/>
       <c r="BI77" s="1"/>
       <c r="BJ77" s="1"/>
-      <c r="BK77" s="1"/>
+      <c r="BK77" s="1" t="s">
+        <v>991</v>
+      </c>
       <c r="BL77" s="1"/>
       <c r="BM77" s="1"/>
       <c r="BN77" s="1"/>
-      <c r="BO77" s="1"/>
+      <c r="BO77" s="1" t="s">
+        <v>992</v>
+      </c>
       <c r="BP77" s="1"/>
       <c r="BQ77" s="1"/>
       <c r="BR77" s="1"/>
@@ -19592,17 +20401,29 @@
       <c r="BY77" s="1"/>
       <c r="BZ77" s="1"/>
       <c r="CA77" s="1"/>
-      <c r="CB77" s="1"/>
-      <c r="CC77" s="1"/>
-      <c r="CD77" s="1"/>
+      <c r="CB77" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="CC77" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="CD77" s="1" t="s">
+        <v>994</v>
+      </c>
       <c r="CE77" s="1"/>
       <c r="CF77" s="1"/>
       <c r="CG77" s="1"/>
       <c r="CH77" s="1"/>
-      <c r="CI77" s="1"/>
-      <c r="CJ77" s="1"/>
+      <c r="CI77" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="CJ77" s="1" t="s">
+        <v>903</v>
+      </c>
       <c r="CK77" s="1"/>
-      <c r="CL77" s="1"/>
+      <c r="CL77" s="1" t="s">
+        <v>995</v>
+      </c>
       <c r="CM77" s="1"/>
       <c r="CN77" s="1"/>
       <c r="CO77" s="1"/>
@@ -19614,9 +20435,11 @@
       <c r="CU77" s="1"/>
       <c r="CV77" s="1"/>
       <c r="CW77" s="1"/>
-      <c r="CX77" s="1"/>
+      <c r="CX77" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="78" spans="1:102" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>41</v>
       </c>
@@ -19633,7 +20456,7 @@
         <v>30</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>219</v>
+        <v>928</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>321</v>
@@ -19699,16 +20522,30 @@
       <c r="AF78" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="AG78" s="1"/>
-      <c r="AH78" s="1"/>
-      <c r="AI78" s="1"/>
+      <c r="AG78" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AH78" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AI78" s="1" t="s">
+        <v>391</v>
+      </c>
       <c r="AJ78" s="1"/>
       <c r="AK78" s="1"/>
-      <c r="AL78" s="1"/>
-      <c r="AM78" s="1"/>
+      <c r="AL78" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="AM78" s="1" t="s">
+        <v>328</v>
+      </c>
       <c r="AN78" s="1"/>
-      <c r="AO78" s="1"/>
-      <c r="AP78" s="1"/>
+      <c r="AO78" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AP78" s="1" t="s">
+        <v>997</v>
+      </c>
       <c r="AQ78" s="1"/>
       <c r="AR78" s="1"/>
       <c r="AS78" s="1"/>
@@ -19718,15 +20555,21 @@
       <c r="AW78" s="1"/>
       <c r="AX78" s="1"/>
       <c r="AY78" s="1"/>
-      <c r="AZ78" s="1"/>
-      <c r="BA78" s="1"/>
+      <c r="AZ78" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="BA78" s="1" t="s">
+        <v>999</v>
+      </c>
       <c r="BB78" s="1"/>
       <c r="BC78" s="1"/>
       <c r="BD78" s="1"/>
       <c r="BE78" s="1"/>
       <c r="BF78" s="1"/>
       <c r="BG78" s="1"/>
-      <c r="BH78" s="1"/>
+      <c r="BH78" s="1" t="s">
+        <v>1001</v>
+      </c>
       <c r="BI78" s="1"/>
       <c r="BJ78" s="1"/>
       <c r="BK78" s="1"/>
@@ -19746,7 +20589,9 @@
       <c r="BY78" s="1"/>
       <c r="BZ78" s="1"/>
       <c r="CA78" s="1"/>
-      <c r="CB78" s="1"/>
+      <c r="CB78" s="1" t="s">
+        <v>1002</v>
+      </c>
       <c r="CC78" s="1"/>
       <c r="CD78" s="1"/>
       <c r="CE78" s="1"/>
@@ -19768,9 +20613,11 @@
       <c r="CU78" s="1"/>
       <c r="CV78" s="1"/>
       <c r="CW78" s="1"/>
-      <c r="CX78" s="1"/>
+      <c r="CX78" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="79" spans="1:102" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>41</v>
       </c>
@@ -19787,7 +20634,7 @@
         <v>30</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>219</v>
+        <v>928</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>321</v>
@@ -19853,16 +20700,30 @@
       <c r="AF79" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="AG79" s="1"/>
-      <c r="AH79" s="1"/>
-      <c r="AI79" s="1"/>
+      <c r="AG79" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AH79" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="AI79" s="1" t="s">
+        <v>391</v>
+      </c>
       <c r="AJ79" s="1"/>
       <c r="AK79" s="1"/>
-      <c r="AL79" s="1"/>
-      <c r="AM79" s="1"/>
+      <c r="AL79" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="AM79" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="AN79" s="1"/>
-      <c r="AO79" s="1"/>
-      <c r="AP79" s="1"/>
+      <c r="AO79" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AP79" s="1" t="s">
+        <v>1005</v>
+      </c>
       <c r="AQ79" s="1"/>
       <c r="AR79" s="1"/>
       <c r="AS79" s="1"/>
@@ -19872,8 +20733,12 @@
       <c r="AW79" s="1"/>
       <c r="AX79" s="1"/>
       <c r="AY79" s="1"/>
-      <c r="AZ79" s="1"/>
-      <c r="BA79" s="1"/>
+      <c r="AZ79" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="BA79" s="1" t="s">
+        <v>1007</v>
+      </c>
       <c r="BB79" s="1"/>
       <c r="BC79" s="1"/>
       <c r="BD79" s="1"/>
@@ -19922,9 +20787,11 @@
       <c r="CU79" s="1"/>
       <c r="CV79" s="1"/>
       <c r="CW79" s="1"/>
-      <c r="CX79" s="1"/>
+      <c r="CX79" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="80" spans="1:102" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A80" s="22"/>
       <c r="B80" s="22"/>
       <c r="C80" s="23"/>
@@ -19952,7 +20819,9 @@
       <c r="U80" s="22"/>
       <c r="V80" s="22"/>
       <c r="W80" s="22"/>
-      <c r="X80" s="22"/>
+      <c r="X80" s="22" t="s">
+        <v>328</v>
+      </c>
       <c r="Y80" s="22" t="s">
         <v>326</v>
       </c>
@@ -19970,7 +20839,9 @@
         <v>115</v>
       </c>
       <c r="AG80" s="22"/>
-      <c r="AH80" s="22"/>
+      <c r="AH80" s="22" t="s">
+        <v>1008</v>
+      </c>
       <c r="AI80" s="22"/>
       <c r="AJ80" s="22"/>
       <c r="AK80" s="22"/>
@@ -19987,23 +20858,33 @@
       <c r="AV80" s="22"/>
       <c r="AW80" s="22"/>
       <c r="AX80" s="22"/>
-      <c r="AY80" s="22"/>
+      <c r="AY80" s="22" t="s">
+        <v>1009</v>
+      </c>
       <c r="AZ80" s="22"/>
       <c r="BA80" s="22"/>
       <c r="BB80" s="22"/>
       <c r="BC80" s="22"/>
       <c r="BD80" s="22"/>
       <c r="BE80" s="22"/>
-      <c r="BF80" s="22"/>
-      <c r="BG80" s="22"/>
-      <c r="BH80" s="22"/>
+      <c r="BF80" s="22" t="s">
+        <v>1018</v>
+      </c>
+      <c r="BG80" s="22" t="s">
+        <v>1019</v>
+      </c>
+      <c r="BH80" s="22" t="s">
+        <v>1011</v>
+      </c>
       <c r="BI80" s="22"/>
       <c r="BJ80" s="22"/>
       <c r="BK80" s="22"/>
       <c r="BL80" s="22"/>
       <c r="BM80" s="22"/>
       <c r="BN80" s="22"/>
-      <c r="BO80" s="22"/>
+      <c r="BO80" s="22" t="s">
+        <v>1014</v>
+      </c>
       <c r="BP80" s="22"/>
       <c r="BQ80" s="22"/>
       <c r="BR80" s="22"/>
@@ -20015,22 +20896,34 @@
       <c r="BX80" s="22"/>
       <c r="BY80" s="22"/>
       <c r="BZ80" s="22"/>
-      <c r="CA80" s="22"/>
+      <c r="CA80" s="22" t="s">
+        <v>1010</v>
+      </c>
       <c r="CB80" s="22"/>
       <c r="CC80" s="22"/>
-      <c r="CD80" s="22"/>
+      <c r="CD80" s="22" t="s">
+        <v>1015</v>
+      </c>
       <c r="CE80" s="22"/>
       <c r="CF80" s="22"/>
       <c r="CG80" s="22"/>
-      <c r="CH80" s="22"/>
+      <c r="CH80" s="22" t="s">
+        <v>1012</v>
+      </c>
       <c r="CI80" s="22"/>
-      <c r="CJ80" s="22"/>
+      <c r="CJ80" s="22" t="s">
+        <v>1013</v>
+      </c>
       <c r="CK80" s="22"/>
       <c r="CL80" s="22"/>
-      <c r="CM80" s="22"/>
+      <c r="CM80" s="22" t="s">
+        <v>1017</v>
+      </c>
       <c r="CN80" s="22"/>
       <c r="CO80" s="22"/>
-      <c r="CP80" s="22"/>
+      <c r="CP80" s="22" t="s">
+        <v>1016</v>
+      </c>
       <c r="CQ80" s="22"/>
       <c r="CR80" s="22"/>
       <c r="CS80" s="22"/>

--- a/Data/PGD/PGD_structuration.xlsx
+++ b/Data/PGD/PGD_structuration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\PGD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D91F32-CF87-4C37-923C-D19C33E8FDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844B42F7-CB3C-4D1F-A2E5-4B96D28D1FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{98FDD2D6-D1A3-4DDF-A839-2A0863A95ED3}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2929" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="1052">
   <si>
     <t>Financeur</t>
   </si>
@@ -4829,6 +4829,257 @@
   <si>
     <t>The  recruitment  of  two  engineers  is  necessary  for  the 
 standardization of the data and the construction of the database</t>
+  </si>
+  <si>
+    <t>Dans un contexte mondial marqué par l'urgence climatique et la nécessité d'atteindre la neutralité
+carbone, les écosystèmes terrestres font face à des défis majeurs, notamment les impacts négatifs du
+changement climatique sur la séquestration du dioxyde de carbone (CO2) par la photosynthèse. Dans
+ce cadre, émergent des enjeux cruciaux liés à la recherche de solutions agricoles visant à atténuer ces
+impacts et à favoriser l'adaptation des cultures, tout en maintenant une forte productivité.
+GREENSCALE propose une approche novatrice axée sur la réduction du besoin en azote des cultures
+comme stratégie d'atténuation et d'adaptation. Le cœur de l'hypothèse du projet repose sur la
+régulation du contenu en chlorophylle [Chl] chez les plantes, un processus naturel influant sur
+l'acclimatation de la photosynthèse aux conditions environnementales. L'objectif est de tester l'idée
+qu'un ajustement spécifique de la chlorophylle b et de ses complexes protéiques associés peut réduire PGD du projet GREENSCALE
+2
+l'assimilation d'azote du sol, diminuer la température du couvert végétal et l'évapotranspiration, sans
+compromettre l'assimilation du CO2 en conditions de lumière non limitante.
+Cette initiative repose sur un partenariat innovant entre des chercheurs de l'INRAE, du CNRS, du CEA
+et d'ARVALIS, avec pour ambition d'approfondir la compréhension des interactions entre la nutrition
+azotée et la photosynthèse, sur le cycle carbone-azote dans le sol, de développer des modèles à
+l'échelle du champ et de l’environnement. En utilisant des variétés de verdissement d'orge non-OGM,
+GREENSCALE explore les réponses biologiques de ces cultures à la sécheresse et à l'azote, et vise à
+améliorer la précision des modèles de surfaces continentales, en particulier pour les terres agricoles
+et les prairies.
+Les résultats attendus orienteront les futurs programmes d'amélioration des plantes, ouvrant ainsi la
+voie à des pratiques agricoles plus durables et résilientes face aux défis environnementaux et aux
+exigences de production céréalières. Au-delà de son impact sur l'agriculture, GREENSCALE s'inscrit
+dans une perspective plus large de structuration de la recherche intégrée en photosynthèse en France.
+En agissant comme un pont entre les recherches moléculaires et cellulaires sur la photosynthèse d'une
+part, et les approches environnementales et agronomiques d'autre part, le projet vise à favoriser la
+collaboration entre différentes spécialités scientifiques et à intégrer des approches complémentaires,
+dépassant ainsi les limites des disciplines individuelles. Ainsi, GREENSCALE se positionne comme une
+initiative novatrice, alliant recherche de pointe, collaboration inter-institutionnelle et engagement en
+faveur de solutions agricoles durables et résilientes face aux défis environnementaux mondiaux.</t>
+  </si>
+  <si>
+    <t>Le projet GREENSCALE vise à produire des données expérimentales permettant d'établir le lien entre
+la teneur en chlorophylle des plantes, les paramètres de la photosynthèse, l'efficacité d'utilisation de
+l'azote (NUE) et la réponse des plantes à des stress abiotiques. Dans ce cadre, les partenaires
+collecteront des données sur la croissance des plantes, leur efficacité d'assimilation du carbone et
+l'utilisation de l'azote</t>
+  </si>
+  <si>
+    <t>Les plantes seront identifiées à l’aide d’un code-barres contenant des informations sur la culture (date,
+lieu, condition de culture), le génotype et le numéro de répétition. L’ensemble des mesures sera
+intégré à un fichier unique respectant le format de sortie du MultiSpeQ, outil qui sera partagé entre
+les différents partenaires du projet</t>
+  </si>
+  <si>
+    <t>Les données produites concerneront :
+• La notation de la croissance (biomasse, taux de croissance relatif, pourcentage d’eau)
+• Des mesures de l’efficacité de la photosynthèse et de l’assimilation du carbone obtenues par
+MultiSpeQ ou Licor
+• Des analyses de l’efficacité d’utilisation de l’azote (%C et %N des tissus, 15N% et 13C%
+isotopiques)
+• Des données protéomiques</t>
+  </si>
+  <si>
+    <t>csv</t>
+  </si>
+  <si>
+    <t>MultispeQ ou Licor</t>
+  </si>
+  <si>
+    <t>36 Mo</t>
+  </si>
+  <si>
+    <t>Les méthodes d’analyse protéomiques seront fournies par la plateforme Protéogen de l’Université de
+Caen.</t>
+  </si>
+  <si>
+    <t>Les données seront accompagnées de métadonnées décrivant les conditions de culture et les
+protocoles de mesure. La méthodologie employée pour les mesures liées à la NUE suivra les standards
+de l’Arabidopsis Trait Ontology (https://doi.org/10.57745/7YO1GF), qui reste valable pour l’orge. De
+plus, les protocoles d’analyse protéomique seront fournis par la plateforme Protéogen de l’Université
+de Caen.</t>
+  </si>
+  <si>
+    <t>Afin de garantir la qualité des données, un contrôle rigoureux sera mis en place comprenant la double
+vérification des entrées manuelles, l’identification des valeurs aberrantes à l’aide de scripts R, ainsi
+que l’usage de formats standardisés pour assurer la cohérence des fichiers.</t>
+  </si>
+  <si>
+    <t>Les métadonnées et les données seront stockées et partagées dans un dossier partagé avec l’ensemble
+des partenaires du projet GREENSCALE. Dans ce dossier, les partenaires vont pouvoir trouver des
+informations à propos de :
+- des documents de présentations (templates, icones),
+- un agenda partagé,
+- des informations sur le matériel végétal,
+- le contrat et le document scientifique soumis au PEPR,
+- les comptes-rendus des réunions mensuels,
+- la littérature scientifique partagée,
+- les protocoles expérimentaux partagés,
+- les informations sur les appareils partagés (MultiSpeQ…),
+- les documents de communications (articles…)
+- les données de résultats d’analyse</t>
+  </si>
+  <si>
+    <t>&amp;Resana&amp;</t>
+  </si>
+  <si>
+    <t>Etalab</t>
+  </si>
+  <si>
+    <t>&amp;Chacun des partenaires conserve la propriété totale et exclusive de ses données antérieures si elles ne
+sont pas du domaine public. Lorsque les données antérieures appartiennent à des tiers auprès
+desquels les Partenaires ont obtenu les droits d’exploitation aux fins de participation au projet
+GREENSCALE, ces données antérieures demeurent la propriété de ces tiers. Les partenaires
+conviennent que les données produites par le projet sont du domaine public et à ce titre exploitables
+librement. Les données seront donc sous licence ouverte ETALAB. Les données devront alors faire
+référence à l’institution dépositaire du spécimen documenté, mais porter la mention du projet comme
+convenu dans le contrat avec l’ANR. Les partenaires conviendront d’un commun accord des mesures
+de protection à prendre concernant les données communes dans le cadre de l’accord de consortium&amp;</t>
+  </si>
+  <si>
+    <t>2 ans d'embargo</t>
+  </si>
+  <si>
+    <t>Pour la durée du projet, le Muséum national d’histoire naturelle à Paris assure la coordination de la
+gestion des données. À terme, les données seront intégrées à l’infrastructure data.gouv.fr, qui est
+reconnue par plusieurs ministères comme une infrastructure Nationale ayant vocation à servir de point
+nodal pour l’accès aux données des collections des données en France</t>
+  </si>
+  <si>
+    <t>The Data Management Plan (DMP) is a key component of the overall
+management of the CLIM-FAS project. It outlines the procedures for
+collecting, processing, utilizing, documenting, and managing data,
+taking into account all stages of the data lifecycle.
+The document also specifies the types of data that will be generated
+within the project, how these data will be shared within the
+consortium, and the methods for making them openly accessible.
+Furthermore, it explains how the CLIM-FAS consortium plans to
+ensure that its research data are findable, accessible, interoperable,
+and reusable (FAIR) to guarantee rigorous data management.
+Finally, this DMP includes a description of the data management policy
+and standards (including metadata) that will be applied</t>
+  </si>
+  <si>
+    <t>CLIM-FAS aims to enhance knowledge on the contribution and
+mitigation potential of the French agricultural sector to climate change
+and to generate scientific evidence on the economic and legal
+effectiveness of public actions designed to promote and accelerate the
+implementation of mitigation solutions. More specifically, it seeks to:
+Estimate GHG sources and sinks in French agriculture under
+current and future climate, considering soil and climatic
+conditions, farm heterogeneity and diversity in farming practices
+Provide evidence on the cost-effectiveness of selected greenhouse
+gas (GHG) mitigation measures (MMs)
+Investigate psychological, socio-economic and legal levers and
+barriers for the uptake of MMs
+Assess mitigation potential of French agriculture and estimate
+heterogeneous marginal abatement costs
+Draw up a critical economic and legal assessment of selected
+existing legal, policy and economic incentives targeting GHG
+sources and sinks and propose improvement and alternatives
+Provide policymakers with evidence based insights and data driven
+recommendations on mitigation strategies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New data will be primarily collected through interviews and surveys tailored to address the project’s specific objectives. These
+surveys will focus on gathering primary data from farmers and stakeholders to identify psychological, socio-economic, and legal
+factors that influence the adoption of mitigation measures (MMs).
+In addition, existing data from reliable sources, such as national databases (e.g., GHG National Inventory, CITEPA, FADN,
+Eurostat) and previous research projects (e.g., INRAE-4pour1000, DSCATT project), will be re-used to support modelling
+experiments, prevent duplication, and ensure efficient resource utilization. These datasets will be carefully evaluated for
+relevance, consistency, and quality before being integrated into the project’s analysis.
+</t>
+  </si>
+  <si>
+    <t>Furthermore, the project will generate new data through model simulations. These simulations will produce datasets that address
+existing knowledge gaps, such as data on carbon fluxes, GHG emissions under current and future climate scenarios, the cost-
+effectiveness of selected MMs, the agricultural sector's mitigation potential, and the impacts of policies, regulations, and economic
+incentives.
+For confidentiality reasons, only aggregated simulation data (farm type, farm size, region) will be shared publicly. Furthermore, no
+statistics will be reported if the data are based on a group fewer than 15 observations.
+To ensure transparency and accessibility, all new, reused, and generated data will be processed, standardized, and documented in
+accordance with FAIR principles (Findable, Accessible, Interoperable, Reusable).
+Metadata will be created to facilitate understanding and reproducibility. The data will be stored in secure repositories accessible
+to project partners and, where possible, to the broader scientific community.</t>
+  </si>
+  <si>
+    <t>type of uses</t>
+  </si>
+  <si>
+    <t>&amp;The project will produce the codes and scripts for the models developed within the project, which can be used, adapted and
+extended in future projects&amp;</t>
+  </si>
+  <si>
+    <t>The metadata accompanying the data will include:
+Descriptive metadata will cover the title, abstract, keywords, authors, and dates of creation and last update.
+Administrative metadata will detail the data owner, access rights, usage rights, and version control.
+Structural metadata will describe the data format, structure, and types.
+Technical metadata will include information on the software/tools used, data collection methods, and data processing steps.
+The datasets will be accompanied by documentations which provide a:
+Comprehensive overview of the data collection methodology, including sampling methods, data sources, and instruments
+used.
+Description of the data organization, including the data model, naming conventions, and data storage.
+Description of data quality control, including error handling, and data cleaning procedures.</t>
+  </si>
+  <si>
+    <t>A set of data quality control measures will be implemented, such as:
+Use of appropriate data storage facilities
+Use of good and harmonized data organization (easy access to files and data)
+Use of free software when possible (e.g. R for statistical analyses and Git for version control).
+Provide metadata &amp; documentation files to make data and code understandable for others.
+...
+CLIM-FAS consortium will also promote the reproducibility of its research findings.</t>
+  </si>
+  <si>
+    <t>A user guide with examples and support information will be provided to assist users in accessing and utilizing the models
+developed with the project.
+Software papers could be envisaged for some models</t>
+  </si>
+  <si>
+    <t>data inrae</t>
+  </si>
+  <si>
+    <t>Access to sensitive (personal) data such as FADN is strictly controlled by the Confenditial Access Portal (CASD) after passing
+through the Secret Committee during and after the research.
+Access to other datasets during the research will be strictly controlled and limited to project members.
+Regular backups of all data will be performed and stored in secure, off-site locations to prevent data loss in case of system
+failures or security breaches.
+Ethical guidelines will be followed to ensure that data is collected, stored, and used in a manner that respects the privacy
+and rights of the individuals involved in the research.</t>
+  </si>
+  <si>
+    <t>Access to farm economic model (codes and database) during the research is controlled by the Confenditial Access Portal
+(CASD)
+Access to ORCHIDEE will be strictly controlled and limited to authorized personnel only. This will be managed through
+secure authentication methods.</t>
+  </si>
+  <si>
+    <t>&amp;Model codes and scripts will be stored and shared among working groups using versioning software (svn or GitLab).
+Svn/Git version control system allows files and data to be tracked synchronized, which allows collaboration and reproducibility&amp;</t>
+  </si>
+  <si>
+    <t>&amp;For the reused data, only FADN contains sensitive (personal) data. Access to these data is strictly controlled by the Confenditial
+Access Portal (CASD) after passing through the Secret Committee.
+For the collected data through interviews, formal contractual agreements will be drawn with actors when necessary, depending on
+how samples are accessed.
+For the collected data through interviews without external actors’ agreement, we will ensure that the conditions for collecting,
+processing and storing data will respect legal requirements on personal data, in line with the General Data Protection Regulation
+(GDPR)&amp;</t>
+  </si>
+  <si>
+    <t>Model codes and scripts will be stored in Software Heritage (https://www.softwareheritage.org/?lang=fr) which ensure long-term
+archiving</t>
+  </si>
+  <si>
+    <t>Both the farm economic model and the DEA model are written in GAMS (General Algebraic Modelling System) language. A
+GAMS licence is needed to change the codes and run the models.
+Statistical software such as Stata or R will be used for analysing survey data. No licence is required for R (free software);
+however, Stata licence is needed to change the code and execute the model.</t>
   </si>
 </sst>
 </file>
@@ -20931,9 +21182,11 @@
       <c r="CU80" s="22"/>
       <c r="CV80" s="22"/>
       <c r="CW80" s="22"/>
-      <c r="CX80" s="22"/>
+      <c r="CX80" s="22" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="81" spans="1:102" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>41</v>
       </c>
@@ -20950,7 +21203,7 @@
         <v>32</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>219</v>
+        <v>1020</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="15">
@@ -21014,15 +21267,21 @@
       <c r="AF81" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AG81" s="1"/>
-      <c r="AH81" s="1"/>
+      <c r="AG81" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AH81" s="1" t="s">
+        <v>1021</v>
+      </c>
       <c r="AI81" s="1"/>
       <c r="AJ81" s="1"/>
       <c r="AK81" s="1"/>
       <c r="AL81" s="1"/>
       <c r="AM81" s="1"/>
       <c r="AN81" s="1"/>
-      <c r="AO81" s="1"/>
+      <c r="AO81" s="1" t="s">
+        <v>396</v>
+      </c>
       <c r="AP81" s="1"/>
       <c r="AQ81" s="1"/>
       <c r="AR81" s="1"/>
@@ -21032,23 +21291,41 @@
       <c r="AV81" s="1"/>
       <c r="AW81" s="1"/>
       <c r="AX81" s="1"/>
-      <c r="AY81" s="1"/>
+      <c r="AY81" s="1" t="s">
+        <v>1023</v>
+      </c>
       <c r="AZ81" s="1"/>
-      <c r="BA81" s="1"/>
-      <c r="BB81" s="1"/>
-      <c r="BC81" s="1"/>
-      <c r="BD81" s="1"/>
-      <c r="BE81" s="1"/>
+      <c r="BA81" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="BB81" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="BC81" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="BD81" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="BE81" s="1" t="s">
+        <v>1027</v>
+      </c>
       <c r="BF81" s="1"/>
       <c r="BG81" s="1"/>
-      <c r="BH81" s="1"/>
+      <c r="BH81" s="1" t="s">
+        <v>1022</v>
+      </c>
       <c r="BI81" s="1"/>
-      <c r="BJ81" s="1"/>
+      <c r="BJ81" s="1" t="s">
+        <v>1028</v>
+      </c>
       <c r="BK81" s="1"/>
       <c r="BL81" s="1"/>
       <c r="BM81" s="1"/>
       <c r="BN81" s="1"/>
-      <c r="BO81" s="1"/>
+      <c r="BO81" s="1" t="s">
+        <v>1029</v>
+      </c>
       <c r="BP81" s="1"/>
       <c r="BQ81" s="1"/>
       <c r="BR81" s="1"/>
@@ -21060,22 +21337,38 @@
       <c r="BX81" s="1"/>
       <c r="BY81" s="1"/>
       <c r="BZ81" s="1"/>
-      <c r="CA81" s="1"/>
-      <c r="CB81" s="1"/>
-      <c r="CC81" s="1"/>
+      <c r="CA81" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="CB81" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="CC81" s="1" t="s">
+        <v>1031</v>
+      </c>
       <c r="CD81" s="1"/>
       <c r="CE81" s="1"/>
       <c r="CF81" s="1"/>
       <c r="CG81" s="1"/>
-      <c r="CH81" s="1"/>
+      <c r="CH81" s="1" t="s">
+        <v>1033</v>
+      </c>
       <c r="CI81" s="1"/>
-      <c r="CJ81" s="1"/>
-      <c r="CK81" s="1"/>
+      <c r="CJ81" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="CK81" s="1" t="s">
+        <v>1034</v>
+      </c>
       <c r="CL81" s="1"/>
       <c r="CM81" s="1"/>
-      <c r="CN81" s="1"/>
+      <c r="CN81" s="1" t="s">
+        <v>1032</v>
+      </c>
       <c r="CO81" s="1"/>
-      <c r="CP81" s="1"/>
+      <c r="CP81" s="1" t="s">
+        <v>1035</v>
+      </c>
       <c r="CQ81" s="1"/>
       <c r="CR81" s="1"/>
       <c r="CS81" s="1"/>
@@ -21083,7 +21376,9 @@
       <c r="CU81" s="1"/>
       <c r="CV81" s="1"/>
       <c r="CW81" s="1"/>
-      <c r="CX81" s="1"/>
+      <c r="CX81" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="82" spans="1:102" ht="58" x14ac:dyDescent="0.35">
       <c r="A82" s="22" t="s">
@@ -21237,7 +21532,7 @@
       <c r="CW82" s="22"/>
       <c r="CX82" s="22"/>
     </row>
-    <row r="83" spans="1:102" ht="116" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>41</v>
       </c>
@@ -21254,7 +21549,7 @@
         <v>34</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>219</v>
+        <v>1037</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>345</v>
@@ -21298,7 +21593,7 @@
         <v>212</v>
       </c>
       <c r="V83" s="1" t="s">
-        <v>219</v>
+        <v>1036</v>
       </c>
       <c r="W83" s="1" t="s">
         <v>343</v>
@@ -21323,61 +21618,97 @@
         <v>115</v>
       </c>
       <c r="AG83" s="1"/>
-      <c r="AH83" s="1"/>
-      <c r="AI83" s="1"/>
+      <c r="AH83" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="AI83" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="AJ83" s="1"/>
       <c r="AK83" s="1"/>
       <c r="AL83" s="1"/>
       <c r="AM83" s="1"/>
       <c r="AN83" s="1"/>
-      <c r="AO83" s="1"/>
+      <c r="AO83" s="1" t="s">
+        <v>396</v>
+      </c>
       <c r="AP83" s="1"/>
-      <c r="AQ83" s="1"/>
-      <c r="AR83" s="1"/>
-      <c r="AS83" s="1"/>
+      <c r="AQ83" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AR83" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AS83" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="AT83" s="1"/>
       <c r="AU83" s="1"/>
       <c r="AV83" s="1"/>
       <c r="AW83" s="1"/>
       <c r="AX83" s="1"/>
-      <c r="AY83" s="1"/>
+      <c r="AY83" s="1" t="s">
+        <v>1039</v>
+      </c>
       <c r="AZ83" s="1"/>
-      <c r="BA83" s="1"/>
-      <c r="BB83" s="1"/>
-      <c r="BC83" s="1"/>
+      <c r="BA83" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="BB83" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="BC83" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="BD83" s="1"/>
       <c r="BE83" s="1"/>
       <c r="BF83" s="1"/>
       <c r="BG83" s="1"/>
-      <c r="BH83" s="1"/>
+      <c r="BH83" s="1" t="s">
+        <v>1042</v>
+      </c>
       <c r="BI83" s="1"/>
       <c r="BJ83" s="1"/>
       <c r="BK83" s="1"/>
       <c r="BL83" s="1"/>
       <c r="BM83" s="1"/>
       <c r="BN83" s="1"/>
-      <c r="BO83" s="1"/>
+      <c r="BO83" s="1" t="s">
+        <v>1043</v>
+      </c>
       <c r="BP83" s="1"/>
       <c r="BQ83" s="1"/>
-      <c r="BR83" s="1"/>
+      <c r="BR83" s="1" t="s">
+        <v>1049</v>
+      </c>
       <c r="BS83" s="1"/>
       <c r="BT83" s="1"/>
       <c r="BU83" s="1"/>
-      <c r="BV83" s="1"/>
+      <c r="BV83" s="1" t="s">
+        <v>1040</v>
+      </c>
       <c r="BW83" s="1"/>
       <c r="BX83" s="1"/>
       <c r="BY83" s="1"/>
       <c r="BZ83" s="1"/>
       <c r="CA83" s="1"/>
-      <c r="CB83" s="1"/>
-      <c r="CC83" s="1"/>
-      <c r="CD83" s="1"/>
+      <c r="CB83" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="CC83" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="CD83" s="1" t="s">
+        <v>1046</v>
+      </c>
       <c r="CE83" s="1"/>
       <c r="CF83" s="1"/>
       <c r="CG83" s="1"/>
       <c r="CH83" s="1"/>
       <c r="CI83" s="1"/>
-      <c r="CJ83" s="1"/>
+      <c r="CJ83" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="CK83" s="1"/>
       <c r="CL83" s="1"/>
       <c r="CM83" s="1"/>
@@ -21391,9 +21722,11 @@
       <c r="CU83" s="1"/>
       <c r="CV83" s="1"/>
       <c r="CW83" s="1"/>
-      <c r="CX83" s="1"/>
+      <c r="CX83" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="84" spans="1:102" ht="116" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>41</v>
       </c>
@@ -21410,7 +21743,7 @@
         <v>34</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>219</v>
+        <v>1037</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>286</v>
@@ -21454,7 +21787,7 @@
         <v>212</v>
       </c>
       <c r="V84" s="1" t="s">
-        <v>219</v>
+        <v>1036</v>
       </c>
       <c r="W84" s="1" t="s">
         <v>343</v>
@@ -21496,20 +21829,32 @@
       <c r="AV84" s="1"/>
       <c r="AW84" s="1"/>
       <c r="AX84" s="1"/>
-      <c r="AY84" s="1"/>
+      <c r="AY84" s="1" t="s">
+        <v>1041</v>
+      </c>
       <c r="AZ84" s="1"/>
-      <c r="BA84" s="1"/>
-      <c r="BB84" s="1"/>
-      <c r="BC84" s="1"/>
+      <c r="BA84" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="BB84" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="BC84" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="BD84" s="1"/>
       <c r="BE84" s="1"/>
       <c r="BF84" s="1"/>
       <c r="BG84" s="1"/>
-      <c r="BH84" s="1"/>
+      <c r="BH84" s="1" t="s">
+        <v>1044</v>
+      </c>
       <c r="BI84" s="1"/>
       <c r="BJ84" s="1"/>
       <c r="BK84" s="1"/>
-      <c r="BL84" s="1"/>
+      <c r="BL84" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="BM84" s="1"/>
       <c r="BN84" s="1"/>
       <c r="BO84" s="1"/>
@@ -21519,21 +21864,33 @@
       <c r="BS84" s="1"/>
       <c r="BT84" s="1"/>
       <c r="BU84" s="1"/>
-      <c r="BV84" s="1"/>
+      <c r="BV84" s="1" t="s">
+        <v>1040</v>
+      </c>
       <c r="BW84" s="1"/>
       <c r="BX84" s="1"/>
       <c r="BY84" s="1"/>
       <c r="BZ84" s="1"/>
       <c r="CA84" s="1"/>
-      <c r="CB84" s="1"/>
+      <c r="CB84" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="CC84" s="1"/>
-      <c r="CD84" s="1"/>
+      <c r="CD84" s="1" t="s">
+        <v>1047</v>
+      </c>
       <c r="CE84" s="1"/>
-      <c r="CF84" s="1"/>
+      <c r="CF84" s="1" t="s">
+        <v>1048</v>
+      </c>
       <c r="CG84" s="1"/>
-      <c r="CH84" s="1"/>
+      <c r="CH84" s="1" t="s">
+        <v>1051</v>
+      </c>
       <c r="CI84" s="1"/>
-      <c r="CJ84" s="1"/>
+      <c r="CJ84" s="1" t="s">
+        <v>1050</v>
+      </c>
       <c r="CK84" s="1"/>
       <c r="CL84" s="1"/>
       <c r="CM84" s="1"/>
@@ -21543,11 +21900,15 @@
       <c r="CQ84" s="1"/>
       <c r="CR84" s="1"/>
       <c r="CS84" s="1"/>
-      <c r="CT84" s="1"/>
+      <c r="CT84" s="1" t="s">
+        <v>1050</v>
+      </c>
       <c r="CU84" s="1"/>
       <c r="CV84" s="1"/>
       <c r="CW84" s="1"/>
-      <c r="CX84" s="1"/>
+      <c r="CX84" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:CP1" xr:uid="{E04D9850-7CF0-4E84-8E6E-B467C0834BD4}"/>

--- a/Data/PGD/PGD_structuration.xlsx
+++ b/Data/PGD/PGD_structuration.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\PGD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844B42F7-CB3C-4D1F-A2E5-4B96D28D1FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CE63ED-F687-4B89-A96A-A83945911CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{98FDD2D6-D1A3-4DDF-A839-2A0863A95ED3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{98FDD2D6-D1A3-4DDF-A839-2A0863A95ED3}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$CP$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$CP$84</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="1052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2986" uniqueCount="1053">
   <si>
     <t>Financeur</t>
   </si>
@@ -5080,6 +5080,9 @@
 GAMS licence is needed to change the codes and run the models.
 Statistical software such as Stata or R will be used for analysing survey data. No licence is required for R (free software);
 however, Stata licence is needed to change the code and execute the model.</t>
+  </si>
+  <si>
+    <t>&amp;questions&amp;</t>
   </si>
 </sst>
 </file>
@@ -21043,8 +21046,12 @@
       </c>
     </row>
     <row r="80" spans="1:102" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A80" s="22"/>
-      <c r="B80" s="22"/>
+      <c r="A80" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="B80" s="22" t="s">
+        <v>1052</v>
+      </c>
       <c r="C80" s="23"/>
       <c r="D80" s="22"/>
       <c r="E80" s="22" t="s">
@@ -21911,7 +21918,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CP1" xr:uid="{E04D9850-7CF0-4E84-8E6E-B467C0834BD4}"/>
+  <autoFilter ref="A1:CP84" xr:uid="{E04D9850-7CF0-4E84-8E6E-B467C0834BD4}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="E3 E14 E42 E57 E52:E54 E71 E63 E65 E61 E80:E83">
     <cfRule type="containsText" dxfId="109" priority="122" operator="containsText" text="INSUFFISANT">
